--- a/customers/abas.xlsx
+++ b/customers/abas.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="202">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -622,6 +622,9 @@
   </si>
   <si>
     <t>وجه تکیه گول</t>
+  </si>
+  <si>
+    <t>پرو شیر گول</t>
   </si>
 </sst>
 </file>
@@ -1136,7 +1139,7 @@
       </c>
       <c r="H2" s="9">
         <f>B180</f>
-        <v>1826000</v>
+        <v>1964000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3588,17 +3591,21 @@
     <row r="176" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="8">
         <f t="shared" si="7"/>
-        <v>1826000</v>
-      </c>
-      <c r="B176" s="8"/>
+        <v>1964000</v>
+      </c>
+      <c r="B176" s="8">
+        <v>138000</v>
+      </c>
       <c r="C176" s="8"/>
-      <c r="D176" s="1"/>
+      <c r="D176" s="1" t="s">
+        <v>201</v>
+      </c>
       <c r="E176" s="1"/>
     </row>
     <row r="177" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="8">
         <f t="shared" si="7"/>
-        <v>1826000</v>
+        <v>1964000</v>
       </c>
       <c r="B177" s="8"/>
       <c r="C177" s="8"/>
@@ -3608,7 +3615,7 @@
     <row r="178" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B178" s="9">
         <f>SUM(B158:B177)+B152</f>
-        <v>9754500</v>
+        <v>9892500</v>
       </c>
       <c r="C178" s="9">
         <f>SUM(C158:C177)+C152</f>
@@ -3619,7 +3626,7 @@
     <row r="180" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B180" s="10">
         <f>A177</f>
-        <v>1826000</v>
+        <v>1964000</v>
       </c>
       <c r="C180" s="12" t="s">
         <v>198</v>

--- a/customers/abas.xlsx
+++ b/customers/abas.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="202">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="H2" s="9">
         <f>B180</f>
-        <v>1964000</v>
+        <v>2104000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3605,17 +3605,21 @@
     <row r="177" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="8">
         <f t="shared" si="7"/>
-        <v>1964000</v>
-      </c>
-      <c r="B177" s="8"/>
+        <v>2104000</v>
+      </c>
+      <c r="B177" s="8">
+        <v>140000</v>
+      </c>
       <c r="C177" s="8"/>
-      <c r="D177" s="1"/>
+      <c r="D177" s="1" t="s">
+        <v>143</v>
+      </c>
       <c r="E177" s="1"/>
     </row>
     <row r="178" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B178" s="9">
         <f>SUM(B158:B177)+B152</f>
-        <v>9892500</v>
+        <v>10032500</v>
       </c>
       <c r="C178" s="9">
         <f>SUM(C158:C177)+C152</f>
@@ -3626,7 +3630,7 @@
     <row r="180" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B180" s="10">
         <f>A177</f>
-        <v>1964000</v>
+        <v>2104000</v>
       </c>
       <c r="C180" s="12" t="s">
         <v>198</v>

--- a/customers/abas.xlsx
+++ b/customers/abas.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="204">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -625,6 +625,12 @@
   </si>
   <si>
     <t>پرو شیر گول</t>
+  </si>
+  <si>
+    <t>1405/04/13</t>
+  </si>
+  <si>
+    <t>بسکویت سیگار</t>
   </si>
 </sst>
 </file>
@@ -740,7 +746,28 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="15">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1138,8 +1165,8 @@
         <v>7</v>
       </c>
       <c r="H2" s="9">
-        <f>B180</f>
-        <v>2104000</v>
+        <f>B206</f>
+        <v>2165000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3645,56 +3672,303 @@
         <v>87</v>
       </c>
     </row>
-    <row r="182" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="183" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="184" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="185" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="186" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="187" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="188" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="189" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="190" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="191" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="192" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="193" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="194" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="195" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="196" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="197" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="198" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="199" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="200" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="201" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="202" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="203" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="204" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="205" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="206" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="207" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="208" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="182" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A182" t="s">
+        <v>10</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C182" s="2"/>
+    </row>
+    <row r="183" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A183" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B183" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C183" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D183" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E183" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A184" s="8">
+        <f>B180+B184-C184</f>
+        <v>2165000</v>
+      </c>
+      <c r="B184" s="8">
+        <v>61000</v>
+      </c>
+      <c r="C184" s="8"/>
+      <c r="D184" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="E184" s="1" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A185" s="8">
+        <f>A184+B185-C185</f>
+        <v>2165000</v>
+      </c>
+      <c r="B185" s="8"/>
+      <c r="C185" s="8"/>
+      <c r="D185" s="1"/>
+      <c r="E185" s="1"/>
+    </row>
+    <row r="186" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A186" s="8">
+        <f t="shared" ref="A186:A203" si="8">A185+B186-C186</f>
+        <v>2165000</v>
+      </c>
+      <c r="B186" s="8"/>
+      <c r="C186" s="8"/>
+      <c r="D186" s="1"/>
+      <c r="E186" s="1"/>
+    </row>
+    <row r="187" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A187" s="8">
+        <f t="shared" si="8"/>
+        <v>2165000</v>
+      </c>
+      <c r="B187" s="8"/>
+      <c r="C187" s="8"/>
+      <c r="D187" s="1"/>
+      <c r="E187" s="1"/>
+    </row>
+    <row r="188" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A188" s="8">
+        <f t="shared" si="8"/>
+        <v>2165000</v>
+      </c>
+      <c r="B188" s="8"/>
+      <c r="C188" s="8"/>
+      <c r="D188" s="1"/>
+      <c r="E188" s="1"/>
+    </row>
+    <row r="189" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A189" s="8">
+        <f t="shared" si="8"/>
+        <v>2165000</v>
+      </c>
+      <c r="B189" s="8"/>
+      <c r="C189" s="8"/>
+      <c r="D189" s="1"/>
+      <c r="E189" s="1"/>
+    </row>
+    <row r="190" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A190" s="8">
+        <f t="shared" si="8"/>
+        <v>2165000</v>
+      </c>
+      <c r="B190" s="8"/>
+      <c r="C190" s="8"/>
+      <c r="D190" s="1"/>
+      <c r="E190" s="1"/>
+    </row>
+    <row r="191" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A191" s="8">
+        <f t="shared" si="8"/>
+        <v>2165000</v>
+      </c>
+      <c r="B191" s="8"/>
+      <c r="C191" s="8"/>
+      <c r="D191" s="1"/>
+      <c r="E191" s="1"/>
+    </row>
+    <row r="192" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A192" s="8">
+        <f t="shared" si="8"/>
+        <v>2165000</v>
+      </c>
+      <c r="B192" s="8"/>
+      <c r="C192" s="8"/>
+      <c r="D192" s="1"/>
+      <c r="E192" s="1"/>
+    </row>
+    <row r="193" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A193" s="8">
+        <f t="shared" si="8"/>
+        <v>2165000</v>
+      </c>
+      <c r="B193" s="8"/>
+      <c r="C193" s="8"/>
+      <c r="D193" s="1"/>
+      <c r="E193" s="1"/>
+    </row>
+    <row r="194" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A194" s="8">
+        <f t="shared" si="8"/>
+        <v>2165000</v>
+      </c>
+      <c r="B194" s="8"/>
+      <c r="C194" s="8"/>
+      <c r="D194" s="1"/>
+      <c r="E194" s="1"/>
+    </row>
+    <row r="195" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A195" s="8">
+        <f t="shared" si="8"/>
+        <v>2165000</v>
+      </c>
+      <c r="B195" s="8"/>
+      <c r="C195" s="8"/>
+      <c r="D195" s="1"/>
+      <c r="E195" s="1"/>
+    </row>
+    <row r="196" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A196" s="8">
+        <f t="shared" si="8"/>
+        <v>2165000</v>
+      </c>
+      <c r="B196" s="8"/>
+      <c r="C196" s="8"/>
+      <c r="D196" s="1"/>
+      <c r="E196" s="1"/>
+    </row>
+    <row r="197" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A197" s="8">
+        <f t="shared" si="8"/>
+        <v>2165000</v>
+      </c>
+      <c r="B197" s="8"/>
+      <c r="C197" s="8"/>
+      <c r="D197" s="1"/>
+      <c r="E197" s="1"/>
+    </row>
+    <row r="198" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A198" s="8">
+        <f t="shared" si="8"/>
+        <v>2165000</v>
+      </c>
+      <c r="B198" s="8"/>
+      <c r="C198" s="8"/>
+      <c r="D198" s="1"/>
+      <c r="E198" s="1"/>
+    </row>
+    <row r="199" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A199" s="8">
+        <f t="shared" si="8"/>
+        <v>2165000</v>
+      </c>
+      <c r="B199" s="8"/>
+      <c r="C199" s="8"/>
+      <c r="D199" s="1"/>
+      <c r="E199" s="1"/>
+    </row>
+    <row r="200" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A200" s="8">
+        <f t="shared" si="8"/>
+        <v>2165000</v>
+      </c>
+      <c r="B200" s="8"/>
+      <c r="C200" s="8"/>
+      <c r="D200" s="1"/>
+      <c r="E200" s="1"/>
+    </row>
+    <row r="201" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A201" s="8">
+        <f t="shared" si="8"/>
+        <v>2165000</v>
+      </c>
+      <c r="B201" s="8"/>
+      <c r="C201" s="8"/>
+      <c r="D201" s="1"/>
+      <c r="E201" s="1"/>
+    </row>
+    <row r="202" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A202" s="8">
+        <f t="shared" si="8"/>
+        <v>2165000</v>
+      </c>
+      <c r="B202" s="8"/>
+      <c r="C202" s="8"/>
+      <c r="D202" s="1"/>
+      <c r="E202" s="1"/>
+    </row>
+    <row r="203" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A203" s="8">
+        <f t="shared" si="8"/>
+        <v>2165000</v>
+      </c>
+      <c r="B203" s="8"/>
+      <c r="C203" s="8"/>
+      <c r="D203" s="1"/>
+      <c r="E203" s="1"/>
+    </row>
+    <row r="204" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B204" s="9">
+        <f>SUM(B184:B203)+B178</f>
+        <v>10093500</v>
+      </c>
+      <c r="C204" s="9">
+        <f>SUM(C184:C203)+C178</f>
+        <v>7928500</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="206" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B206" s="10">
+        <f>A203</f>
+        <v>2165000</v>
+      </c>
+      <c r="C206" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="D206" s="12"/>
+    </row>
+    <row r="207" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B207" t="s">
+        <v>88</v>
+      </c>
+      <c r="D207" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="209" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="210" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="211" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="212" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="C102:D102"/>
     <mergeCell ref="C128:D128"/>
     <mergeCell ref="C154:D154"/>
     <mergeCell ref="C180:D180"/>
+    <mergeCell ref="C206:D206"/>
   </mergeCells>
   <conditionalFormatting sqref="B102">
-    <cfRule type="cellIs" dxfId="11" priority="12" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="14" priority="15" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="13" priority="14" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="12" priority="13" operator="lessThanOrEqual">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B128">
+    <cfRule type="cellIs" dxfId="11" priority="10" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="10" priority="11" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="10" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="9" priority="12" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B128">
+  <conditionalFormatting sqref="B154">
     <cfRule type="cellIs" dxfId="8" priority="7" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3705,7 +3979,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B154">
+  <conditionalFormatting sqref="B180">
     <cfRule type="cellIs" dxfId="5" priority="4" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3716,7 +3990,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B180">
+  <conditionalFormatting sqref="B206">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>

--- a/customers/abas.xlsx
+++ b/customers/abas.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="205">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -631,6 +631,9 @@
   </si>
   <si>
     <t>بسکویت سیگار</t>
+  </si>
+  <si>
+    <t>1405/04/14</t>
   </si>
 </sst>
 </file>
@@ -1166,7 +1169,7 @@
       </c>
       <c r="H2" s="9">
         <f>B206</f>
-        <v>2165000</v>
+        <v>2382000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3717,17 +3720,23 @@
     <row r="185" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="8">
         <f>A184+B185-C185</f>
-        <v>2165000</v>
-      </c>
-      <c r="B185" s="8"/>
+        <v>2382000</v>
+      </c>
+      <c r="B185" s="8">
+        <v>217000</v>
+      </c>
       <c r="C185" s="8"/>
-      <c r="D185" s="1"/>
-      <c r="E185" s="1"/>
+      <c r="D185" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E185" s="1" t="s">
+        <v>204</v>
+      </c>
     </row>
     <row r="186" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="8">
         <f t="shared" ref="A186:A203" si="8">A185+B186-C186</f>
-        <v>2165000</v>
+        <v>2382000</v>
       </c>
       <c r="B186" s="8"/>
       <c r="C186" s="8"/>
@@ -3737,7 +3746,7 @@
     <row r="187" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="8">
         <f t="shared" si="8"/>
-        <v>2165000</v>
+        <v>2382000</v>
       </c>
       <c r="B187" s="8"/>
       <c r="C187" s="8"/>
@@ -3747,7 +3756,7 @@
     <row r="188" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="8">
         <f t="shared" si="8"/>
-        <v>2165000</v>
+        <v>2382000</v>
       </c>
       <c r="B188" s="8"/>
       <c r="C188" s="8"/>
@@ -3757,7 +3766,7 @@
     <row r="189" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="8">
         <f t="shared" si="8"/>
-        <v>2165000</v>
+        <v>2382000</v>
       </c>
       <c r="B189" s="8"/>
       <c r="C189" s="8"/>
@@ -3767,7 +3776,7 @@
     <row r="190" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="8">
         <f t="shared" si="8"/>
-        <v>2165000</v>
+        <v>2382000</v>
       </c>
       <c r="B190" s="8"/>
       <c r="C190" s="8"/>
@@ -3777,7 +3786,7 @@
     <row r="191" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="8">
         <f t="shared" si="8"/>
-        <v>2165000</v>
+        <v>2382000</v>
       </c>
       <c r="B191" s="8"/>
       <c r="C191" s="8"/>
@@ -3787,7 +3796,7 @@
     <row r="192" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="8">
         <f t="shared" si="8"/>
-        <v>2165000</v>
+        <v>2382000</v>
       </c>
       <c r="B192" s="8"/>
       <c r="C192" s="8"/>
@@ -3797,7 +3806,7 @@
     <row r="193" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="8">
         <f t="shared" si="8"/>
-        <v>2165000</v>
+        <v>2382000</v>
       </c>
       <c r="B193" s="8"/>
       <c r="C193" s="8"/>
@@ -3807,7 +3816,7 @@
     <row r="194" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="8">
         <f t="shared" si="8"/>
-        <v>2165000</v>
+        <v>2382000</v>
       </c>
       <c r="B194" s="8"/>
       <c r="C194" s="8"/>
@@ -3817,7 +3826,7 @@
     <row r="195" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="8">
         <f t="shared" si="8"/>
-        <v>2165000</v>
+        <v>2382000</v>
       </c>
       <c r="B195" s="8"/>
       <c r="C195" s="8"/>
@@ -3827,7 +3836,7 @@
     <row r="196" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="8">
         <f t="shared" si="8"/>
-        <v>2165000</v>
+        <v>2382000</v>
       </c>
       <c r="B196" s="8"/>
       <c r="C196" s="8"/>
@@ -3837,7 +3846,7 @@
     <row r="197" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="8">
         <f t="shared" si="8"/>
-        <v>2165000</v>
+        <v>2382000</v>
       </c>
       <c r="B197" s="8"/>
       <c r="C197" s="8"/>
@@ -3847,7 +3856,7 @@
     <row r="198" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="8">
         <f t="shared" si="8"/>
-        <v>2165000</v>
+        <v>2382000</v>
       </c>
       <c r="B198" s="8"/>
       <c r="C198" s="8"/>
@@ -3857,7 +3866,7 @@
     <row r="199" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="8">
         <f t="shared" si="8"/>
-        <v>2165000</v>
+        <v>2382000</v>
       </c>
       <c r="B199" s="8"/>
       <c r="C199" s="8"/>
@@ -3867,7 +3876,7 @@
     <row r="200" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="8">
         <f t="shared" si="8"/>
-        <v>2165000</v>
+        <v>2382000</v>
       </c>
       <c r="B200" s="8"/>
       <c r="C200" s="8"/>
@@ -3877,7 +3886,7 @@
     <row r="201" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="8">
         <f t="shared" si="8"/>
-        <v>2165000</v>
+        <v>2382000</v>
       </c>
       <c r="B201" s="8"/>
       <c r="C201" s="8"/>
@@ -3887,7 +3896,7 @@
     <row r="202" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="8">
         <f t="shared" si="8"/>
-        <v>2165000</v>
+        <v>2382000</v>
       </c>
       <c r="B202" s="8"/>
       <c r="C202" s="8"/>
@@ -3897,7 +3906,7 @@
     <row r="203" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="8">
         <f t="shared" si="8"/>
-        <v>2165000</v>
+        <v>2382000</v>
       </c>
       <c r="B203" s="8"/>
       <c r="C203" s="8"/>
@@ -3907,7 +3916,7 @@
     <row r="204" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B204" s="9">
         <f>SUM(B184:B203)+B178</f>
-        <v>10093500</v>
+        <v>10310500</v>
       </c>
       <c r="C204" s="9">
         <f>SUM(C184:C203)+C178</f>
@@ -3918,7 +3927,7 @@
     <row r="206" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B206" s="10">
         <f>A203</f>
-        <v>2165000</v>
+        <v>2382000</v>
       </c>
       <c r="C206" s="12" t="s">
         <v>198</v>

--- a/customers/abas.xlsx
+++ b/customers/abas.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="206">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -634,6 +634,9 @@
   </si>
   <si>
     <t>1405/04/14</t>
+  </si>
+  <si>
+    <t>کرانچی گچ گچ آب</t>
   </si>
 </sst>
 </file>
@@ -1169,7 +1172,7 @@
       </c>
       <c r="H2" s="9">
         <f>B206</f>
-        <v>2382000</v>
+        <v>2522000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3736,17 +3739,21 @@
     <row r="186" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="8">
         <f t="shared" ref="A186:A203" si="8">A185+B186-C186</f>
-        <v>2382000</v>
-      </c>
-      <c r="B186" s="8"/>
+        <v>2522000</v>
+      </c>
+      <c r="B186" s="8">
+        <v>140000</v>
+      </c>
       <c r="C186" s="8"/>
-      <c r="D186" s="1"/>
+      <c r="D186" s="1" t="s">
+        <v>205</v>
+      </c>
       <c r="E186" s="1"/>
     </row>
     <row r="187" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="8">
         <f t="shared" si="8"/>
-        <v>2382000</v>
+        <v>2522000</v>
       </c>
       <c r="B187" s="8"/>
       <c r="C187" s="8"/>
@@ -3756,7 +3763,7 @@
     <row r="188" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="8">
         <f t="shared" si="8"/>
-        <v>2382000</v>
+        <v>2522000</v>
       </c>
       <c r="B188" s="8"/>
       <c r="C188" s="8"/>
@@ -3766,7 +3773,7 @@
     <row r="189" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="8">
         <f t="shared" si="8"/>
-        <v>2382000</v>
+        <v>2522000</v>
       </c>
       <c r="B189" s="8"/>
       <c r="C189" s="8"/>
@@ -3776,7 +3783,7 @@
     <row r="190" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="8">
         <f t="shared" si="8"/>
-        <v>2382000</v>
+        <v>2522000</v>
       </c>
       <c r="B190" s="8"/>
       <c r="C190" s="8"/>
@@ -3786,7 +3793,7 @@
     <row r="191" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="8">
         <f t="shared" si="8"/>
-        <v>2382000</v>
+        <v>2522000</v>
       </c>
       <c r="B191" s="8"/>
       <c r="C191" s="8"/>
@@ -3796,7 +3803,7 @@
     <row r="192" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="8">
         <f t="shared" si="8"/>
-        <v>2382000</v>
+        <v>2522000</v>
       </c>
       <c r="B192" s="8"/>
       <c r="C192" s="8"/>
@@ -3806,7 +3813,7 @@
     <row r="193" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="8">
         <f t="shared" si="8"/>
-        <v>2382000</v>
+        <v>2522000</v>
       </c>
       <c r="B193" s="8"/>
       <c r="C193" s="8"/>
@@ -3816,7 +3823,7 @@
     <row r="194" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="8">
         <f t="shared" si="8"/>
-        <v>2382000</v>
+        <v>2522000</v>
       </c>
       <c r="B194" s="8"/>
       <c r="C194" s="8"/>
@@ -3826,7 +3833,7 @@
     <row r="195" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="8">
         <f t="shared" si="8"/>
-        <v>2382000</v>
+        <v>2522000</v>
       </c>
       <c r="B195" s="8"/>
       <c r="C195" s="8"/>
@@ -3836,7 +3843,7 @@
     <row r="196" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="8">
         <f t="shared" si="8"/>
-        <v>2382000</v>
+        <v>2522000</v>
       </c>
       <c r="B196" s="8"/>
       <c r="C196" s="8"/>
@@ -3846,7 +3853,7 @@
     <row r="197" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="8">
         <f t="shared" si="8"/>
-        <v>2382000</v>
+        <v>2522000</v>
       </c>
       <c r="B197" s="8"/>
       <c r="C197" s="8"/>
@@ -3856,7 +3863,7 @@
     <row r="198" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="8">
         <f t="shared" si="8"/>
-        <v>2382000</v>
+        <v>2522000</v>
       </c>
       <c r="B198" s="8"/>
       <c r="C198" s="8"/>
@@ -3866,7 +3873,7 @@
     <row r="199" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="8">
         <f t="shared" si="8"/>
-        <v>2382000</v>
+        <v>2522000</v>
       </c>
       <c r="B199" s="8"/>
       <c r="C199" s="8"/>
@@ -3876,7 +3883,7 @@
     <row r="200" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="8">
         <f t="shared" si="8"/>
-        <v>2382000</v>
+        <v>2522000</v>
       </c>
       <c r="B200" s="8"/>
       <c r="C200" s="8"/>
@@ -3886,7 +3893,7 @@
     <row r="201" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="8">
         <f t="shared" si="8"/>
-        <v>2382000</v>
+        <v>2522000</v>
       </c>
       <c r="B201" s="8"/>
       <c r="C201" s="8"/>
@@ -3896,7 +3903,7 @@
     <row r="202" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="8">
         <f t="shared" si="8"/>
-        <v>2382000</v>
+        <v>2522000</v>
       </c>
       <c r="B202" s="8"/>
       <c r="C202" s="8"/>
@@ -3906,7 +3913,7 @@
     <row r="203" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="8">
         <f t="shared" si="8"/>
-        <v>2382000</v>
+        <v>2522000</v>
       </c>
       <c r="B203" s="8"/>
       <c r="C203" s="8"/>
@@ -3916,7 +3923,7 @@
     <row r="204" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B204" s="9">
         <f>SUM(B184:B203)+B178</f>
-        <v>10310500</v>
+        <v>10450500</v>
       </c>
       <c r="C204" s="9">
         <f>SUM(C184:C203)+C178</f>
@@ -3927,7 +3934,7 @@
     <row r="206" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B206" s="10">
         <f>A203</f>
-        <v>2382000</v>
+        <v>2522000</v>
       </c>
       <c r="C206" s="12" t="s">
         <v>198</v>

--- a/customers/abas.xlsx
+++ b/customers/abas.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="207">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -637,6 +637,9 @@
   </si>
   <si>
     <t>کرانچی گچ گچ آب</t>
+  </si>
+  <si>
+    <t>1405/4/17</t>
   </si>
 </sst>
 </file>
@@ -1172,7 +1175,7 @@
       </c>
       <c r="H2" s="9">
         <f>B206</f>
-        <v>2522000</v>
+        <v>2634000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3753,17 +3756,23 @@
     <row r="187" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="8">
         <f t="shared" si="8"/>
-        <v>2522000</v>
-      </c>
-      <c r="B187" s="8"/>
+        <v>2634000</v>
+      </c>
+      <c r="B187" s="8">
+        <v>112000</v>
+      </c>
       <c r="C187" s="8"/>
-      <c r="D187" s="1"/>
-      <c r="E187" s="1"/>
+      <c r="D187" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E187" s="1" t="s">
+        <v>206</v>
+      </c>
     </row>
     <row r="188" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="8">
         <f t="shared" si="8"/>
-        <v>2522000</v>
+        <v>2634000</v>
       </c>
       <c r="B188" s="8"/>
       <c r="C188" s="8"/>
@@ -3773,7 +3782,7 @@
     <row r="189" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="8">
         <f t="shared" si="8"/>
-        <v>2522000</v>
+        <v>2634000</v>
       </c>
       <c r="B189" s="8"/>
       <c r="C189" s="8"/>
@@ -3783,7 +3792,7 @@
     <row r="190" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="8">
         <f t="shared" si="8"/>
-        <v>2522000</v>
+        <v>2634000</v>
       </c>
       <c r="B190" s="8"/>
       <c r="C190" s="8"/>
@@ -3793,7 +3802,7 @@
     <row r="191" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="8">
         <f t="shared" si="8"/>
-        <v>2522000</v>
+        <v>2634000</v>
       </c>
       <c r="B191" s="8"/>
       <c r="C191" s="8"/>
@@ -3803,7 +3812,7 @@
     <row r="192" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="8">
         <f t="shared" si="8"/>
-        <v>2522000</v>
+        <v>2634000</v>
       </c>
       <c r="B192" s="8"/>
       <c r="C192" s="8"/>
@@ -3813,7 +3822,7 @@
     <row r="193" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="8">
         <f t="shared" si="8"/>
-        <v>2522000</v>
+        <v>2634000</v>
       </c>
       <c r="B193" s="8"/>
       <c r="C193" s="8"/>
@@ -3823,7 +3832,7 @@
     <row r="194" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="8">
         <f t="shared" si="8"/>
-        <v>2522000</v>
+        <v>2634000</v>
       </c>
       <c r="B194" s="8"/>
       <c r="C194" s="8"/>
@@ -3833,7 +3842,7 @@
     <row r="195" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="8">
         <f t="shared" si="8"/>
-        <v>2522000</v>
+        <v>2634000</v>
       </c>
       <c r="B195" s="8"/>
       <c r="C195" s="8"/>
@@ -3843,7 +3852,7 @@
     <row r="196" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="8">
         <f t="shared" si="8"/>
-        <v>2522000</v>
+        <v>2634000</v>
       </c>
       <c r="B196" s="8"/>
       <c r="C196" s="8"/>
@@ -3853,7 +3862,7 @@
     <row r="197" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="8">
         <f t="shared" si="8"/>
-        <v>2522000</v>
+        <v>2634000</v>
       </c>
       <c r="B197" s="8"/>
       <c r="C197" s="8"/>
@@ -3863,7 +3872,7 @@
     <row r="198" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="8">
         <f t="shared" si="8"/>
-        <v>2522000</v>
+        <v>2634000</v>
       </c>
       <c r="B198" s="8"/>
       <c r="C198" s="8"/>
@@ -3873,7 +3882,7 @@
     <row r="199" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="8">
         <f t="shared" si="8"/>
-        <v>2522000</v>
+        <v>2634000</v>
       </c>
       <c r="B199" s="8"/>
       <c r="C199" s="8"/>
@@ -3883,7 +3892,7 @@
     <row r="200" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="8">
         <f t="shared" si="8"/>
-        <v>2522000</v>
+        <v>2634000</v>
       </c>
       <c r="B200" s="8"/>
       <c r="C200" s="8"/>
@@ -3893,7 +3902,7 @@
     <row r="201" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="8">
         <f t="shared" si="8"/>
-        <v>2522000</v>
+        <v>2634000</v>
       </c>
       <c r="B201" s="8"/>
       <c r="C201" s="8"/>
@@ -3903,7 +3912,7 @@
     <row r="202" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="8">
         <f t="shared" si="8"/>
-        <v>2522000</v>
+        <v>2634000</v>
       </c>
       <c r="B202" s="8"/>
       <c r="C202" s="8"/>
@@ -3913,7 +3922,7 @@
     <row r="203" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="8">
         <f t="shared" si="8"/>
-        <v>2522000</v>
+        <v>2634000</v>
       </c>
       <c r="B203" s="8"/>
       <c r="C203" s="8"/>
@@ -3923,7 +3932,7 @@
     <row r="204" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B204" s="9">
         <f>SUM(B184:B203)+B178</f>
-        <v>10450500</v>
+        <v>10562500</v>
       </c>
       <c r="C204" s="9">
         <f>SUM(C184:C203)+C178</f>
@@ -3934,7 +3943,7 @@
     <row r="206" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B206" s="10">
         <f>A203</f>
-        <v>2522000</v>
+        <v>2634000</v>
       </c>
       <c r="C206" s="12" t="s">
         <v>198</v>

--- a/customers/abas.xlsx
+++ b/customers/abas.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="212">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -640,6 +640,21 @@
   </si>
   <si>
     <t>1405/4/17</t>
+  </si>
+  <si>
+    <t>1405/04/19</t>
+  </si>
+  <si>
+    <t>گولبازی</t>
+  </si>
+  <si>
+    <t>کیک رضا</t>
+  </si>
+  <si>
+    <t>ساندویچ باغ ممد جواد</t>
+  </si>
+  <si>
+    <t>وجه نون سنگک</t>
   </si>
 </sst>
 </file>
@@ -1175,7 +1190,7 @@
       </c>
       <c r="H2" s="9">
         <f>B206</f>
-        <v>2634000</v>
+        <v>2567000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3772,47 +3787,65 @@
     <row r="188" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="8">
         <f t="shared" si="8"/>
-        <v>2634000</v>
-      </c>
-      <c r="B188" s="8"/>
+        <v>2736000</v>
+      </c>
+      <c r="B188" s="8">
+        <v>102000</v>
+      </c>
       <c r="C188" s="8"/>
-      <c r="D188" s="1"/>
-      <c r="E188" s="1"/>
+      <c r="D188" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="E188" s="1" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="189" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="8">
         <f t="shared" si="8"/>
-        <v>2634000</v>
-      </c>
-      <c r="B189" s="8"/>
+        <v>2821000</v>
+      </c>
+      <c r="B189" s="8">
+        <v>85000</v>
+      </c>
       <c r="C189" s="8"/>
-      <c r="D189" s="1"/>
+      <c r="D189" s="1" t="s">
+        <v>209</v>
+      </c>
       <c r="E189" s="1"/>
     </row>
     <row r="190" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="8">
         <f t="shared" si="8"/>
-        <v>2634000</v>
-      </c>
-      <c r="B190" s="8"/>
+        <v>2967000</v>
+      </c>
+      <c r="B190" s="8">
+        <v>146000</v>
+      </c>
       <c r="C190" s="8"/>
-      <c r="D190" s="1"/>
+      <c r="D190" s="1" t="s">
+        <v>210</v>
+      </c>
       <c r="E190" s="1"/>
     </row>
     <row r="191" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="8">
         <f t="shared" si="8"/>
-        <v>2634000</v>
+        <v>2567000</v>
       </c>
       <c r="B191" s="8"/>
-      <c r="C191" s="8"/>
-      <c r="D191" s="1"/>
+      <c r="C191" s="8">
+        <v>400000</v>
+      </c>
+      <c r="D191" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="E191" s="1"/>
     </row>
     <row r="192" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="8">
         <f t="shared" si="8"/>
-        <v>2634000</v>
+        <v>2567000</v>
       </c>
       <c r="B192" s="8"/>
       <c r="C192" s="8"/>
@@ -3822,7 +3855,7 @@
     <row r="193" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="8">
         <f t="shared" si="8"/>
-        <v>2634000</v>
+        <v>2567000</v>
       </c>
       <c r="B193" s="8"/>
       <c r="C193" s="8"/>
@@ -3832,7 +3865,7 @@
     <row r="194" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="8">
         <f t="shared" si="8"/>
-        <v>2634000</v>
+        <v>2567000</v>
       </c>
       <c r="B194" s="8"/>
       <c r="C194" s="8"/>
@@ -3842,7 +3875,7 @@
     <row r="195" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="8">
         <f t="shared" si="8"/>
-        <v>2634000</v>
+        <v>2567000</v>
       </c>
       <c r="B195" s="8"/>
       <c r="C195" s="8"/>
@@ -3852,7 +3885,7 @@
     <row r="196" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="8">
         <f t="shared" si="8"/>
-        <v>2634000</v>
+        <v>2567000</v>
       </c>
       <c r="B196" s="8"/>
       <c r="C196" s="8"/>
@@ -3862,7 +3895,7 @@
     <row r="197" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="8">
         <f t="shared" si="8"/>
-        <v>2634000</v>
+        <v>2567000</v>
       </c>
       <c r="B197" s="8"/>
       <c r="C197" s="8"/>
@@ -3872,7 +3905,7 @@
     <row r="198" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="8">
         <f t="shared" si="8"/>
-        <v>2634000</v>
+        <v>2567000</v>
       </c>
       <c r="B198" s="8"/>
       <c r="C198" s="8"/>
@@ -3882,7 +3915,7 @@
     <row r="199" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="8">
         <f t="shared" si="8"/>
-        <v>2634000</v>
+        <v>2567000</v>
       </c>
       <c r="B199" s="8"/>
       <c r="C199" s="8"/>
@@ -3892,7 +3925,7 @@
     <row r="200" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="8">
         <f t="shared" si="8"/>
-        <v>2634000</v>
+        <v>2567000</v>
       </c>
       <c r="B200" s="8"/>
       <c r="C200" s="8"/>
@@ -3902,7 +3935,7 @@
     <row r="201" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="8">
         <f t="shared" si="8"/>
-        <v>2634000</v>
+        <v>2567000</v>
       </c>
       <c r="B201" s="8"/>
       <c r="C201" s="8"/>
@@ -3912,7 +3945,7 @@
     <row r="202" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="8">
         <f t="shared" si="8"/>
-        <v>2634000</v>
+        <v>2567000</v>
       </c>
       <c r="B202" s="8"/>
       <c r="C202" s="8"/>
@@ -3922,7 +3955,7 @@
     <row r="203" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="8">
         <f t="shared" si="8"/>
-        <v>2634000</v>
+        <v>2567000</v>
       </c>
       <c r="B203" s="8"/>
       <c r="C203" s="8"/>
@@ -3932,18 +3965,18 @@
     <row r="204" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B204" s="9">
         <f>SUM(B184:B203)+B178</f>
-        <v>10562500</v>
+        <v>10895500</v>
       </c>
       <c r="C204" s="9">
         <f>SUM(C184:C203)+C178</f>
-        <v>7928500</v>
+        <v>8328500</v>
       </c>
     </row>
     <row r="205" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="206" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B206" s="10">
         <f>A203</f>
-        <v>2634000</v>
+        <v>2567000</v>
       </c>
       <c r="C206" s="12" t="s">
         <v>198</v>

--- a/customers/abas.xlsx
+++ b/customers/abas.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="213">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -655,6 +655,9 @@
   </si>
   <si>
     <t>وجه نون سنگک</t>
+  </si>
+  <si>
+    <t>1405/04/22</t>
   </si>
 </sst>
 </file>
@@ -1190,7 +1193,7 @@
       </c>
       <c r="H2" s="9">
         <f>B206</f>
-        <v>2567000</v>
+        <v>2617000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3845,17 +3848,23 @@
     <row r="192" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="8">
         <f t="shared" si="8"/>
-        <v>2567000</v>
-      </c>
-      <c r="B192" s="8"/>
+        <v>2617000</v>
+      </c>
+      <c r="B192" s="8">
+        <v>50000</v>
+      </c>
       <c r="C192" s="8"/>
-      <c r="D192" s="1"/>
-      <c r="E192" s="1"/>
+      <c r="D192" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E192" s="1" t="s">
+        <v>212</v>
+      </c>
     </row>
     <row r="193" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="8">
         <f t="shared" si="8"/>
-        <v>2567000</v>
+        <v>2617000</v>
       </c>
       <c r="B193" s="8"/>
       <c r="C193" s="8"/>
@@ -3865,7 +3874,7 @@
     <row r="194" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="8">
         <f t="shared" si="8"/>
-        <v>2567000</v>
+        <v>2617000</v>
       </c>
       <c r="B194" s="8"/>
       <c r="C194" s="8"/>
@@ -3875,7 +3884,7 @@
     <row r="195" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="8">
         <f t="shared" si="8"/>
-        <v>2567000</v>
+        <v>2617000</v>
       </c>
       <c r="B195" s="8"/>
       <c r="C195" s="8"/>
@@ -3885,7 +3894,7 @@
     <row r="196" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="8">
         <f t="shared" si="8"/>
-        <v>2567000</v>
+        <v>2617000</v>
       </c>
       <c r="B196" s="8"/>
       <c r="C196" s="8"/>
@@ -3895,7 +3904,7 @@
     <row r="197" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="8">
         <f t="shared" si="8"/>
-        <v>2567000</v>
+        <v>2617000</v>
       </c>
       <c r="B197" s="8"/>
       <c r="C197" s="8"/>
@@ -3905,7 +3914,7 @@
     <row r="198" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="8">
         <f t="shared" si="8"/>
-        <v>2567000</v>
+        <v>2617000</v>
       </c>
       <c r="B198" s="8"/>
       <c r="C198" s="8"/>
@@ -3915,7 +3924,7 @@
     <row r="199" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="8">
         <f t="shared" si="8"/>
-        <v>2567000</v>
+        <v>2617000</v>
       </c>
       <c r="B199" s="8"/>
       <c r="C199" s="8"/>
@@ -3925,7 +3934,7 @@
     <row r="200" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="8">
         <f t="shared" si="8"/>
-        <v>2567000</v>
+        <v>2617000</v>
       </c>
       <c r="B200" s="8"/>
       <c r="C200" s="8"/>
@@ -3935,7 +3944,7 @@
     <row r="201" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="8">
         <f t="shared" si="8"/>
-        <v>2567000</v>
+        <v>2617000</v>
       </c>
       <c r="B201" s="8"/>
       <c r="C201" s="8"/>
@@ -3945,7 +3954,7 @@
     <row r="202" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="8">
         <f t="shared" si="8"/>
-        <v>2567000</v>
+        <v>2617000</v>
       </c>
       <c r="B202" s="8"/>
       <c r="C202" s="8"/>
@@ -3955,7 +3964,7 @@
     <row r="203" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="8">
         <f t="shared" si="8"/>
-        <v>2567000</v>
+        <v>2617000</v>
       </c>
       <c r="B203" s="8"/>
       <c r="C203" s="8"/>
@@ -3965,7 +3974,7 @@
     <row r="204" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B204" s="9">
         <f>SUM(B184:B203)+B178</f>
-        <v>10895500</v>
+        <v>10945500</v>
       </c>
       <c r="C204" s="9">
         <f>SUM(C184:C203)+C178</f>
@@ -3976,7 +3985,7 @@
     <row r="206" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B206" s="10">
         <f>A203</f>
-        <v>2567000</v>
+        <v>2617000</v>
       </c>
       <c r="C206" s="12" t="s">
         <v>198</v>

--- a/customers/abas.xlsx
+++ b/customers/abas.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="215">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -658,6 +658,12 @@
   </si>
   <si>
     <t>1405/04/22</t>
+  </si>
+  <si>
+    <t>1405/04/24</t>
+  </si>
+  <si>
+    <t>بیسکوییت سیگار</t>
   </si>
 </sst>
 </file>
@@ -1193,7 +1199,7 @@
       </c>
       <c r="H2" s="9">
         <f>B206</f>
-        <v>2617000</v>
+        <v>2745000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3864,27 +3870,37 @@
     <row r="193" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="8">
         <f t="shared" si="8"/>
-        <v>2617000</v>
-      </c>
-      <c r="B193" s="8"/>
+        <v>2692000</v>
+      </c>
+      <c r="B193" s="8">
+        <v>75000</v>
+      </c>
       <c r="C193" s="8"/>
-      <c r="D193" s="1"/>
-      <c r="E193" s="1"/>
+      <c r="D193" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E193" s="1" t="s">
+        <v>213</v>
+      </c>
     </row>
     <row r="194" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="8">
         <f t="shared" si="8"/>
-        <v>2617000</v>
-      </c>
-      <c r="B194" s="8"/>
+        <v>2745000</v>
+      </c>
+      <c r="B194" s="8">
+        <v>53000</v>
+      </c>
       <c r="C194" s="8"/>
-      <c r="D194" s="1"/>
+      <c r="D194" s="1" t="s">
+        <v>214</v>
+      </c>
       <c r="E194" s="1"/>
     </row>
     <row r="195" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="8">
         <f t="shared" si="8"/>
-        <v>2617000</v>
+        <v>2745000</v>
       </c>
       <c r="B195" s="8"/>
       <c r="C195" s="8"/>
@@ -3894,7 +3910,7 @@
     <row r="196" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="8">
         <f t="shared" si="8"/>
-        <v>2617000</v>
+        <v>2745000</v>
       </c>
       <c r="B196" s="8"/>
       <c r="C196" s="8"/>
@@ -3904,7 +3920,7 @@
     <row r="197" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="8">
         <f t="shared" si="8"/>
-        <v>2617000</v>
+        <v>2745000</v>
       </c>
       <c r="B197" s="8"/>
       <c r="C197" s="8"/>
@@ -3914,7 +3930,7 @@
     <row r="198" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="8">
         <f t="shared" si="8"/>
-        <v>2617000</v>
+        <v>2745000</v>
       </c>
       <c r="B198" s="8"/>
       <c r="C198" s="8"/>
@@ -3924,7 +3940,7 @@
     <row r="199" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="8">
         <f t="shared" si="8"/>
-        <v>2617000</v>
+        <v>2745000</v>
       </c>
       <c r="B199" s="8"/>
       <c r="C199" s="8"/>
@@ -3934,7 +3950,7 @@
     <row r="200" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="8">
         <f t="shared" si="8"/>
-        <v>2617000</v>
+        <v>2745000</v>
       </c>
       <c r="B200" s="8"/>
       <c r="C200" s="8"/>
@@ -3944,7 +3960,7 @@
     <row r="201" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="8">
         <f t="shared" si="8"/>
-        <v>2617000</v>
+        <v>2745000</v>
       </c>
       <c r="B201" s="8"/>
       <c r="C201" s="8"/>
@@ -3954,7 +3970,7 @@
     <row r="202" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="8">
         <f t="shared" si="8"/>
-        <v>2617000</v>
+        <v>2745000</v>
       </c>
       <c r="B202" s="8"/>
       <c r="C202" s="8"/>
@@ -3964,7 +3980,7 @@
     <row r="203" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="8">
         <f t="shared" si="8"/>
-        <v>2617000</v>
+        <v>2745000</v>
       </c>
       <c r="B203" s="8"/>
       <c r="C203" s="8"/>
@@ -3974,7 +3990,7 @@
     <row r="204" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B204" s="9">
         <f>SUM(B184:B203)+B178</f>
-        <v>10945500</v>
+        <v>11073500</v>
       </c>
       <c r="C204" s="9">
         <f>SUM(C184:C203)+C178</f>
@@ -3985,7 +4001,7 @@
     <row r="206" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B206" s="10">
         <f>A203</f>
-        <v>2617000</v>
+        <v>2745000</v>
       </c>
       <c r="C206" s="12" t="s">
         <v>198</v>

--- a/customers/abas.xlsx
+++ b/customers/abas.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="216">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -664,6 +664,9 @@
   </si>
   <si>
     <t>بیسکوییت سیگار</t>
+  </si>
+  <si>
+    <t>1405/04/27</t>
   </si>
 </sst>
 </file>
@@ -1199,7 +1202,7 @@
       </c>
       <c r="H2" s="9">
         <f>B206</f>
-        <v>2745000</v>
+        <v>2795000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3900,17 +3903,23 @@
     <row r="195" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="8">
         <f t="shared" si="8"/>
-        <v>2745000</v>
-      </c>
-      <c r="B195" s="8"/>
+        <v>2795000</v>
+      </c>
+      <c r="B195" s="8">
+        <v>50000</v>
+      </c>
       <c r="C195" s="8"/>
-      <c r="D195" s="1"/>
-      <c r="E195" s="1"/>
+      <c r="D195" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E195" s="1" t="s">
+        <v>215</v>
+      </c>
     </row>
     <row r="196" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="8">
         <f t="shared" si="8"/>
-        <v>2745000</v>
+        <v>2795000</v>
       </c>
       <c r="B196" s="8"/>
       <c r="C196" s="8"/>
@@ -3920,7 +3929,7 @@
     <row r="197" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="8">
         <f t="shared" si="8"/>
-        <v>2745000</v>
+        <v>2795000</v>
       </c>
       <c r="B197" s="8"/>
       <c r="C197" s="8"/>
@@ -3930,7 +3939,7 @@
     <row r="198" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="8">
         <f t="shared" si="8"/>
-        <v>2745000</v>
+        <v>2795000</v>
       </c>
       <c r="B198" s="8"/>
       <c r="C198" s="8"/>
@@ -3940,7 +3949,7 @@
     <row r="199" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="8">
         <f t="shared" si="8"/>
-        <v>2745000</v>
+        <v>2795000</v>
       </c>
       <c r="B199" s="8"/>
       <c r="C199" s="8"/>
@@ -3950,7 +3959,7 @@
     <row r="200" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="8">
         <f t="shared" si="8"/>
-        <v>2745000</v>
+        <v>2795000</v>
       </c>
       <c r="B200" s="8"/>
       <c r="C200" s="8"/>
@@ -3960,7 +3969,7 @@
     <row r="201" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="8">
         <f t="shared" si="8"/>
-        <v>2745000</v>
+        <v>2795000</v>
       </c>
       <c r="B201" s="8"/>
       <c r="C201" s="8"/>
@@ -3970,7 +3979,7 @@
     <row r="202" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="8">
         <f t="shared" si="8"/>
-        <v>2745000</v>
+        <v>2795000</v>
       </c>
       <c r="B202" s="8"/>
       <c r="C202" s="8"/>
@@ -3980,7 +3989,7 @@
     <row r="203" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="8">
         <f t="shared" si="8"/>
-        <v>2745000</v>
+        <v>2795000</v>
       </c>
       <c r="B203" s="8"/>
       <c r="C203" s="8"/>
@@ -3990,7 +3999,7 @@
     <row r="204" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B204" s="9">
         <f>SUM(B184:B203)+B178</f>
-        <v>11073500</v>
+        <v>11123500</v>
       </c>
       <c r="C204" s="9">
         <f>SUM(C184:C203)+C178</f>
@@ -4001,7 +4010,7 @@
     <row r="206" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B206" s="10">
         <f>A203</f>
-        <v>2745000</v>
+        <v>2795000</v>
       </c>
       <c r="C206" s="12" t="s">
         <v>198</v>

--- a/customers/abas.xlsx
+++ b/customers/abas.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="216">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="H2" s="9">
         <f>B206</f>
-        <v>2795000</v>
+        <v>2957000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3919,17 +3919,21 @@
     <row r="196" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="8">
         <f t="shared" si="8"/>
-        <v>2795000</v>
-      </c>
-      <c r="B196" s="8"/>
+        <v>2957000</v>
+      </c>
+      <c r="B196" s="8">
+        <v>162000</v>
+      </c>
       <c r="C196" s="8"/>
-      <c r="D196" s="1"/>
+      <c r="D196" s="1" t="s">
+        <v>143</v>
+      </c>
       <c r="E196" s="1"/>
     </row>
     <row r="197" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="8">
         <f t="shared" si="8"/>
-        <v>2795000</v>
+        <v>2957000</v>
       </c>
       <c r="B197" s="8"/>
       <c r="C197" s="8"/>
@@ -3939,7 +3943,7 @@
     <row r="198" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="8">
         <f t="shared" si="8"/>
-        <v>2795000</v>
+        <v>2957000</v>
       </c>
       <c r="B198" s="8"/>
       <c r="C198" s="8"/>
@@ -3949,7 +3953,7 @@
     <row r="199" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="8">
         <f t="shared" si="8"/>
-        <v>2795000</v>
+        <v>2957000</v>
       </c>
       <c r="B199" s="8"/>
       <c r="C199" s="8"/>
@@ -3959,7 +3963,7 @@
     <row r="200" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="8">
         <f t="shared" si="8"/>
-        <v>2795000</v>
+        <v>2957000</v>
       </c>
       <c r="B200" s="8"/>
       <c r="C200" s="8"/>
@@ -3969,7 +3973,7 @@
     <row r="201" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="8">
         <f t="shared" si="8"/>
-        <v>2795000</v>
+        <v>2957000</v>
       </c>
       <c r="B201" s="8"/>
       <c r="C201" s="8"/>
@@ -3979,7 +3983,7 @@
     <row r="202" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="8">
         <f t="shared" si="8"/>
-        <v>2795000</v>
+        <v>2957000</v>
       </c>
       <c r="B202" s="8"/>
       <c r="C202" s="8"/>
@@ -3989,7 +3993,7 @@
     <row r="203" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="8">
         <f t="shared" si="8"/>
-        <v>2795000</v>
+        <v>2957000</v>
       </c>
       <c r="B203" s="8"/>
       <c r="C203" s="8"/>
@@ -3999,7 +4003,7 @@
     <row r="204" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B204" s="9">
         <f>SUM(B184:B203)+B178</f>
-        <v>11123500</v>
+        <v>11285500</v>
       </c>
       <c r="C204" s="9">
         <f>SUM(C184:C203)+C178</f>
@@ -4010,7 +4014,7 @@
     <row r="206" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B206" s="10">
         <f>A203</f>
-        <v>2795000</v>
+        <v>2957000</v>
       </c>
       <c r="C206" s="12" t="s">
         <v>198</v>

--- a/customers/abas.xlsx
+++ b/customers/abas.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="218">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -667,6 +667,12 @@
   </si>
   <si>
     <t>1405/04/27</t>
+  </si>
+  <si>
+    <t>1405/04/29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">وجه پول </t>
   </si>
 </sst>
 </file>
@@ -1202,7 +1208,7 @@
       </c>
       <c r="H2" s="9">
         <f>B206</f>
-        <v>2957000</v>
+        <v>2837000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3933,17 +3939,23 @@
     <row r="197" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="8">
         <f t="shared" si="8"/>
-        <v>2957000</v>
+        <v>2837000</v>
       </c>
       <c r="B197" s="8"/>
-      <c r="C197" s="8"/>
-      <c r="D197" s="1"/>
-      <c r="E197" s="1"/>
+      <c r="C197" s="8">
+        <v>120000</v>
+      </c>
+      <c r="D197" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="E197" s="1" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="198" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="8">
         <f t="shared" si="8"/>
-        <v>2957000</v>
+        <v>2837000</v>
       </c>
       <c r="B198" s="8"/>
       <c r="C198" s="8"/>
@@ -3953,7 +3965,7 @@
     <row r="199" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="8">
         <f t="shared" si="8"/>
-        <v>2957000</v>
+        <v>2837000</v>
       </c>
       <c r="B199" s="8"/>
       <c r="C199" s="8"/>
@@ -3963,7 +3975,7 @@
     <row r="200" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="8">
         <f t="shared" si="8"/>
-        <v>2957000</v>
+        <v>2837000</v>
       </c>
       <c r="B200" s="8"/>
       <c r="C200" s="8"/>
@@ -3973,7 +3985,7 @@
     <row r="201" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="8">
         <f t="shared" si="8"/>
-        <v>2957000</v>
+        <v>2837000</v>
       </c>
       <c r="B201" s="8"/>
       <c r="C201" s="8"/>
@@ -3983,7 +3995,7 @@
     <row r="202" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="8">
         <f t="shared" si="8"/>
-        <v>2957000</v>
+        <v>2837000</v>
       </c>
       <c r="B202" s="8"/>
       <c r="C202" s="8"/>
@@ -3993,7 +4005,7 @@
     <row r="203" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="8">
         <f t="shared" si="8"/>
-        <v>2957000</v>
+        <v>2837000</v>
       </c>
       <c r="B203" s="8"/>
       <c r="C203" s="8"/>
@@ -4007,14 +4019,14 @@
       </c>
       <c r="C204" s="9">
         <f>SUM(C184:C203)+C178</f>
-        <v>8328500</v>
+        <v>8448500</v>
       </c>
     </row>
     <row r="205" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="206" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B206" s="10">
         <f>A203</f>
-        <v>2957000</v>
+        <v>2837000</v>
       </c>
       <c r="C206" s="12" t="s">
         <v>198</v>

--- a/customers/abas.xlsx
+++ b/customers/abas.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="219">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -673,6 +673,9 @@
   </si>
   <si>
     <t xml:space="preserve">وجه پول </t>
+  </si>
+  <si>
+    <t>1405/04/31</t>
   </si>
 </sst>
 </file>
@@ -1208,7 +1211,7 @@
       </c>
       <c r="H2" s="9">
         <f>B206</f>
-        <v>2837000</v>
+        <v>3087000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3955,17 +3958,23 @@
     <row r="198" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="8">
         <f t="shared" si="8"/>
-        <v>2837000</v>
-      </c>
-      <c r="B198" s="8"/>
+        <v>3087000</v>
+      </c>
+      <c r="B198" s="8">
+        <v>250000</v>
+      </c>
       <c r="C198" s="8"/>
-      <c r="D198" s="1"/>
-      <c r="E198" s="1"/>
+      <c r="D198" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E198" s="1" t="s">
+        <v>218</v>
+      </c>
     </row>
     <row r="199" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="8">
         <f t="shared" si="8"/>
-        <v>2837000</v>
+        <v>3087000</v>
       </c>
       <c r="B199" s="8"/>
       <c r="C199" s="8"/>
@@ -3975,7 +3984,7 @@
     <row r="200" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="8">
         <f t="shared" si="8"/>
-        <v>2837000</v>
+        <v>3087000</v>
       </c>
       <c r="B200" s="8"/>
       <c r="C200" s="8"/>
@@ -3985,7 +3994,7 @@
     <row r="201" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="8">
         <f t="shared" si="8"/>
-        <v>2837000</v>
+        <v>3087000</v>
       </c>
       <c r="B201" s="8"/>
       <c r="C201" s="8"/>
@@ -3995,7 +4004,7 @@
     <row r="202" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="8">
         <f t="shared" si="8"/>
-        <v>2837000</v>
+        <v>3087000</v>
       </c>
       <c r="B202" s="8"/>
       <c r="C202" s="8"/>
@@ -4005,7 +4014,7 @@
     <row r="203" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="8">
         <f t="shared" si="8"/>
-        <v>2837000</v>
+        <v>3087000</v>
       </c>
       <c r="B203" s="8"/>
       <c r="C203" s="8"/>
@@ -4015,7 +4024,7 @@
     <row r="204" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B204" s="9">
         <f>SUM(B184:B203)+B178</f>
-        <v>11285500</v>
+        <v>11535500</v>
       </c>
       <c r="C204" s="9">
         <f>SUM(C184:C203)+C178</f>
@@ -4026,7 +4035,7 @@
     <row r="206" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B206" s="10">
         <f>A203</f>
-        <v>2837000</v>
+        <v>3087000</v>
       </c>
       <c r="C206" s="12" t="s">
         <v>198</v>

--- a/customers/abas.xlsx
+++ b/customers/abas.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="220">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -676,6 +676,9 @@
   </si>
   <si>
     <t>1405/04/31</t>
+  </si>
+  <si>
+    <t>1405/05/01</t>
   </si>
 </sst>
 </file>
@@ -1211,7 +1214,7 @@
       </c>
       <c r="H2" s="9">
         <f>B206</f>
-        <v>3087000</v>
+        <v>2837000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3974,17 +3977,23 @@
     <row r="199" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="8">
         <f t="shared" si="8"/>
-        <v>3087000</v>
+        <v>2837000</v>
       </c>
       <c r="B199" s="8"/>
-      <c r="C199" s="8"/>
-      <c r="D199" s="1"/>
-      <c r="E199" s="1"/>
+      <c r="C199" s="8">
+        <v>250000</v>
+      </c>
+      <c r="D199" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="E199" s="1" t="s">
+        <v>219</v>
+      </c>
     </row>
     <row r="200" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="8">
         <f t="shared" si="8"/>
-        <v>3087000</v>
+        <v>2837000</v>
       </c>
       <c r="B200" s="8"/>
       <c r="C200" s="8"/>
@@ -3994,7 +4003,7 @@
     <row r="201" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="8">
         <f t="shared" si="8"/>
-        <v>3087000</v>
+        <v>2837000</v>
       </c>
       <c r="B201" s="8"/>
       <c r="C201" s="8"/>
@@ -4004,7 +4013,7 @@
     <row r="202" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="8">
         <f t="shared" si="8"/>
-        <v>3087000</v>
+        <v>2837000</v>
       </c>
       <c r="B202" s="8"/>
       <c r="C202" s="8"/>
@@ -4014,7 +4023,7 @@
     <row r="203" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="8">
         <f t="shared" si="8"/>
-        <v>3087000</v>
+        <v>2837000</v>
       </c>
       <c r="B203" s="8"/>
       <c r="C203" s="8"/>
@@ -4028,14 +4037,14 @@
       </c>
       <c r="C204" s="9">
         <f>SUM(C184:C203)+C178</f>
-        <v>8448500</v>
+        <v>8698500</v>
       </c>
     </row>
     <row r="205" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="206" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B206" s="10">
         <f>A203</f>
-        <v>3087000</v>
+        <v>2837000</v>
       </c>
       <c r="C206" s="12" t="s">
         <v>198</v>

--- a/customers/abas.xlsx
+++ b/customers/abas.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="221">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -679,6 +679,9 @@
   </si>
   <si>
     <t>1405/05/01</t>
+  </si>
+  <si>
+    <t>1405/05/09</t>
   </si>
 </sst>
 </file>
@@ -1214,7 +1217,7 @@
       </c>
       <c r="H2" s="9">
         <f>B206</f>
-        <v>2837000</v>
+        <v>2999000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3993,17 +3996,23 @@
     <row r="200" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="8">
         <f t="shared" si="8"/>
-        <v>2837000</v>
-      </c>
-      <c r="B200" s="8"/>
+        <v>2999000</v>
+      </c>
+      <c r="B200" s="8">
+        <v>162000</v>
+      </c>
       <c r="C200" s="8"/>
-      <c r="D200" s="1"/>
-      <c r="E200" s="1"/>
+      <c r="D200" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E200" s="1" t="s">
+        <v>220</v>
+      </c>
     </row>
     <row r="201" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="8">
         <f t="shared" si="8"/>
-        <v>2837000</v>
+        <v>2999000</v>
       </c>
       <c r="B201" s="8"/>
       <c r="C201" s="8"/>
@@ -4013,7 +4022,7 @@
     <row r="202" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="8">
         <f t="shared" si="8"/>
-        <v>2837000</v>
+        <v>2999000</v>
       </c>
       <c r="B202" s="8"/>
       <c r="C202" s="8"/>
@@ -4023,7 +4032,7 @@
     <row r="203" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="8">
         <f t="shared" si="8"/>
-        <v>2837000</v>
+        <v>2999000</v>
       </c>
       <c r="B203" s="8"/>
       <c r="C203" s="8"/>
@@ -4033,7 +4042,7 @@
     <row r="204" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B204" s="9">
         <f>SUM(B184:B203)+B178</f>
-        <v>11535500</v>
+        <v>11697500</v>
       </c>
       <c r="C204" s="9">
         <f>SUM(C184:C203)+C178</f>
@@ -4044,7 +4053,7 @@
     <row r="206" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B206" s="10">
         <f>A203</f>
-        <v>2837000</v>
+        <v>2999000</v>
       </c>
       <c r="C206" s="12" t="s">
         <v>198</v>

--- a/customers/abas.xlsx
+++ b/customers/abas.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="223">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -682,6 +682,12 @@
   </si>
   <si>
     <t>1405/05/09</t>
+  </si>
+  <si>
+    <t>1405/05/10</t>
+  </si>
+  <si>
+    <t>بستنی موزی</t>
   </si>
 </sst>
 </file>
@@ -1217,7 +1223,7 @@
       </c>
       <c r="H2" s="9">
         <f>B206</f>
-        <v>2999000</v>
+        <v>3049000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4012,17 +4018,23 @@
     <row r="201" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="8">
         <f t="shared" si="8"/>
-        <v>2999000</v>
-      </c>
-      <c r="B201" s="8"/>
+        <v>3049000</v>
+      </c>
+      <c r="B201" s="8">
+        <v>50000</v>
+      </c>
       <c r="C201" s="8"/>
-      <c r="D201" s="1"/>
-      <c r="E201" s="1"/>
+      <c r="D201" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="E201" s="1" t="s">
+        <v>221</v>
+      </c>
     </row>
     <row r="202" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="8">
         <f t="shared" si="8"/>
-        <v>2999000</v>
+        <v>3049000</v>
       </c>
       <c r="B202" s="8"/>
       <c r="C202" s="8"/>
@@ -4032,7 +4044,7 @@
     <row r="203" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="8">
         <f t="shared" si="8"/>
-        <v>2999000</v>
+        <v>3049000</v>
       </c>
       <c r="B203" s="8"/>
       <c r="C203" s="8"/>
@@ -4042,7 +4054,7 @@
     <row r="204" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B204" s="9">
         <f>SUM(B184:B203)+B178</f>
-        <v>11697500</v>
+        <v>11747500</v>
       </c>
       <c r="C204" s="9">
         <f>SUM(C184:C203)+C178</f>
@@ -4053,7 +4065,7 @@
     <row r="206" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B206" s="10">
         <f>A203</f>
-        <v>2999000</v>
+        <v>3049000</v>
       </c>
       <c r="C206" s="12" t="s">
         <v>198</v>

--- a/customers/abas.xlsx
+++ b/customers/abas.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="225">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -688,6 +688,12 @@
   </si>
   <si>
     <t>بستنی موزی</t>
+  </si>
+  <si>
+    <t>1405/05/11</t>
+  </si>
+  <si>
+    <t>وجه پول انتخاب واحد</t>
   </si>
 </sst>
 </file>
@@ -1223,7 +1229,7 @@
       </c>
       <c r="H2" s="9">
         <f>B206</f>
-        <v>3049000</v>
+        <v>2549000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4034,17 +4040,23 @@
     <row r="202" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="8">
         <f t="shared" si="8"/>
-        <v>3049000</v>
+        <v>2549000</v>
       </c>
       <c r="B202" s="8"/>
-      <c r="C202" s="8"/>
-      <c r="D202" s="1"/>
-      <c r="E202" s="1"/>
+      <c r="C202" s="8">
+        <v>500000</v>
+      </c>
+      <c r="D202" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="E202" s="1" t="s">
+        <v>223</v>
+      </c>
     </row>
     <row r="203" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="8">
         <f t="shared" si="8"/>
-        <v>3049000</v>
+        <v>2549000</v>
       </c>
       <c r="B203" s="8"/>
       <c r="C203" s="8"/>
@@ -4058,14 +4070,14 @@
       </c>
       <c r="C204" s="9">
         <f>SUM(C184:C203)+C178</f>
-        <v>8698500</v>
+        <v>9198500</v>
       </c>
     </row>
     <row r="205" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="206" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B206" s="10">
         <f>A203</f>
-        <v>3049000</v>
+        <v>2549000</v>
       </c>
       <c r="C206" s="12" t="s">
         <v>198</v>

--- a/customers/abas.xlsx
+++ b/customers/abas.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="227">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -694,6 +694,12 @@
   </si>
   <si>
     <t>وجه پول انتخاب واحد</t>
+  </si>
+  <si>
+    <t>1405/05/13</t>
+  </si>
+  <si>
+    <t>گول بازی دنگ باغ دامو مزه</t>
   </si>
 </sst>
 </file>
@@ -1229,7 +1235,7 @@
       </c>
       <c r="H2" s="9">
         <f>B206</f>
-        <v>2549000</v>
+        <v>2808000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4056,17 +4062,23 @@
     <row r="203" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="8">
         <f t="shared" si="8"/>
-        <v>2549000</v>
-      </c>
-      <c r="B203" s="8"/>
+        <v>2808000</v>
+      </c>
+      <c r="B203" s="8">
+        <v>259000</v>
+      </c>
       <c r="C203" s="8"/>
-      <c r="D203" s="1"/>
-      <c r="E203" s="1"/>
+      <c r="D203" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="E203" s="1" t="s">
+        <v>225</v>
+      </c>
     </row>
     <row r="204" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B204" s="9">
         <f>SUM(B184:B203)+B178</f>
-        <v>11747500</v>
+        <v>12006500</v>
       </c>
       <c r="C204" s="9">
         <f>SUM(C184:C203)+C178</f>
@@ -4077,7 +4089,7 @@
     <row r="206" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B206" s="10">
         <f>A203</f>
-        <v>2549000</v>
+        <v>2808000</v>
       </c>
       <c r="C206" s="12" t="s">
         <v>198</v>

--- a/customers/abas.xlsx
+++ b/customers/abas.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="229">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -700,6 +700,12 @@
   </si>
   <si>
     <t>گول بازی دنگ باغ دامو مزه</t>
+  </si>
+  <si>
+    <t>1405/05/17</t>
+  </si>
+  <si>
+    <t>کیک</t>
   </si>
 </sst>
 </file>
@@ -815,7 +821,28 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="15">
+  <dxfs count="18">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1197,7 +1224,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H212"/>
+  <dimension ref="A1:H264"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.625" customWidth="1"/>
@@ -1234,8 +1261,8 @@
         <v>7</v>
       </c>
       <c r="H2" s="9">
-        <f>B206</f>
-        <v>2808000</v>
+        <f>B232</f>
+        <v>2908000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4104,13 +4131,301 @@
         <v>87</v>
       </c>
     </row>
-    <row r="208" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="209" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="210" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="211" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="212" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="208" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A208" t="s">
+        <v>10</v>
+      </c>
+      <c r="B208" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C208" s="2"/>
+    </row>
+    <row r="209" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A209" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B209" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C209" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D209" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E209" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A210" s="8">
+        <f>B206+B210-C210</f>
+        <v>2908000</v>
+      </c>
+      <c r="B210" s="8">
+        <v>100000</v>
+      </c>
+      <c r="C210" s="8"/>
+      <c r="D210" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="E210" s="1" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A211" s="8">
+        <f>A210+B211-C211</f>
+        <v>2908000</v>
+      </c>
+      <c r="B211" s="8"/>
+      <c r="C211" s="8"/>
+      <c r="D211" s="1"/>
+      <c r="E211" s="1"/>
+    </row>
+    <row r="212" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A212" s="8">
+        <f t="shared" ref="A212:A229" si="9">A211+B212-C212</f>
+        <v>2908000</v>
+      </c>
+      <c r="B212" s="8"/>
+      <c r="C212" s="8"/>
+      <c r="D212" s="1"/>
+      <c r="E212" s="1"/>
+    </row>
+    <row r="213" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A213" s="8">
+        <f t="shared" si="9"/>
+        <v>2908000</v>
+      </c>
+      <c r="B213" s="8"/>
+      <c r="C213" s="8"/>
+      <c r="D213" s="1"/>
+      <c r="E213" s="1"/>
+    </row>
+    <row r="214" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A214" s="8">
+        <f t="shared" si="9"/>
+        <v>2908000</v>
+      </c>
+      <c r="B214" s="8"/>
+      <c r="C214" s="8"/>
+      <c r="D214" s="1"/>
+      <c r="E214" s="1"/>
+    </row>
+    <row r="215" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A215" s="8">
+        <f t="shared" si="9"/>
+        <v>2908000</v>
+      </c>
+      <c r="B215" s="8"/>
+      <c r="C215" s="8"/>
+      <c r="D215" s="1"/>
+      <c r="E215" s="1"/>
+    </row>
+    <row r="216" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A216" s="8">
+        <f t="shared" si="9"/>
+        <v>2908000</v>
+      </c>
+      <c r="B216" s="8"/>
+      <c r="C216" s="8"/>
+      <c r="D216" s="1"/>
+      <c r="E216" s="1"/>
+    </row>
+    <row r="217" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A217" s="8">
+        <f t="shared" si="9"/>
+        <v>2908000</v>
+      </c>
+      <c r="B217" s="8"/>
+      <c r="C217" s="8"/>
+      <c r="D217" s="1"/>
+      <c r="E217" s="1"/>
+    </row>
+    <row r="218" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A218" s="8">
+        <f t="shared" si="9"/>
+        <v>2908000</v>
+      </c>
+      <c r="B218" s="8"/>
+      <c r="C218" s="8"/>
+      <c r="D218" s="1"/>
+      <c r="E218" s="1"/>
+    </row>
+    <row r="219" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A219" s="8">
+        <f t="shared" si="9"/>
+        <v>2908000</v>
+      </c>
+      <c r="B219" s="8"/>
+      <c r="C219" s="8"/>
+      <c r="D219" s="1"/>
+      <c r="E219" s="1"/>
+    </row>
+    <row r="220" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A220" s="8">
+        <f t="shared" si="9"/>
+        <v>2908000</v>
+      </c>
+      <c r="B220" s="8"/>
+      <c r="C220" s="8"/>
+      <c r="D220" s="1"/>
+      <c r="E220" s="1"/>
+    </row>
+    <row r="221" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A221" s="8">
+        <f t="shared" si="9"/>
+        <v>2908000</v>
+      </c>
+      <c r="B221" s="8"/>
+      <c r="C221" s="8"/>
+      <c r="D221" s="1"/>
+      <c r="E221" s="1"/>
+    </row>
+    <row r="222" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A222" s="8">
+        <f t="shared" si="9"/>
+        <v>2908000</v>
+      </c>
+      <c r="B222" s="8"/>
+      <c r="C222" s="8"/>
+      <c r="D222" s="1"/>
+      <c r="E222" s="1"/>
+    </row>
+    <row r="223" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A223" s="8">
+        <f t="shared" si="9"/>
+        <v>2908000</v>
+      </c>
+      <c r="B223" s="8"/>
+      <c r="C223" s="8"/>
+      <c r="D223" s="1"/>
+      <c r="E223" s="1"/>
+    </row>
+    <row r="224" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A224" s="8">
+        <f t="shared" si="9"/>
+        <v>2908000</v>
+      </c>
+      <c r="B224" s="8"/>
+      <c r="C224" s="8"/>
+      <c r="D224" s="1"/>
+      <c r="E224" s="1"/>
+    </row>
+    <row r="225" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A225" s="8">
+        <f t="shared" si="9"/>
+        <v>2908000</v>
+      </c>
+      <c r="B225" s="8"/>
+      <c r="C225" s="8"/>
+      <c r="D225" s="1"/>
+      <c r="E225" s="1"/>
+    </row>
+    <row r="226" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A226" s="8">
+        <f t="shared" si="9"/>
+        <v>2908000</v>
+      </c>
+      <c r="B226" s="8"/>
+      <c r="C226" s="8"/>
+      <c r="D226" s="1"/>
+      <c r="E226" s="1"/>
+    </row>
+    <row r="227" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A227" s="8">
+        <f t="shared" si="9"/>
+        <v>2908000</v>
+      </c>
+      <c r="B227" s="8"/>
+      <c r="C227" s="8"/>
+      <c r="D227" s="1"/>
+      <c r="E227" s="1"/>
+    </row>
+    <row r="228" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A228" s="8">
+        <f t="shared" si="9"/>
+        <v>2908000</v>
+      </c>
+      <c r="B228" s="8"/>
+      <c r="C228" s="8"/>
+      <c r="D228" s="1"/>
+      <c r="E228" s="1"/>
+    </row>
+    <row r="229" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A229" s="8">
+        <f t="shared" si="9"/>
+        <v>2908000</v>
+      </c>
+      <c r="B229" s="8"/>
+      <c r="C229" s="8"/>
+      <c r="D229" s="1"/>
+      <c r="E229" s="1"/>
+    </row>
+    <row r="230" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B230" s="9">
+        <f>SUM(B210:B229)+B204</f>
+        <v>12106500</v>
+      </c>
+      <c r="C230" s="9">
+        <f>SUM(C210:C229)+C204</f>
+        <v>9198500</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="232" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B232" s="10">
+        <f>A229</f>
+        <v>2908000</v>
+      </c>
+      <c r="C232" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="D232" s="12"/>
+    </row>
+    <row r="233" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B233" t="s">
+        <v>88</v>
+      </c>
+      <c r="D233" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="235" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="236" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="237" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="238" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="239" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="240" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="241" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="242" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="243" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="244" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="245" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="246" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="247" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="248" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="249" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="250" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="251" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="252" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="253" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="254" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="255" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="256" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="257" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="258" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="259" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="260" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="261" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="262" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="263" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="264" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
+    <mergeCell ref="C232:D232"/>
     <mergeCell ref="C102:D102"/>
     <mergeCell ref="C128:D128"/>
     <mergeCell ref="C154:D154"/>
@@ -4118,17 +4433,28 @@
     <mergeCell ref="C206:D206"/>
   </mergeCells>
   <conditionalFormatting sqref="B102">
-    <cfRule type="cellIs" dxfId="14" priority="15" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="17" priority="18" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="16" priority="17" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="15" priority="16" operator="lessThanOrEqual">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B128">
+    <cfRule type="cellIs" dxfId="14" priority="13" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="13" priority="14" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="13" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="12" priority="15" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B128">
+  <conditionalFormatting sqref="B154">
     <cfRule type="cellIs" dxfId="11" priority="10" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4139,7 +4465,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B154">
+  <conditionalFormatting sqref="B180">
     <cfRule type="cellIs" dxfId="8" priority="7" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4150,7 +4476,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B180">
+  <conditionalFormatting sqref="B206">
     <cfRule type="cellIs" dxfId="5" priority="4" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4161,7 +4487,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B206">
+  <conditionalFormatting sqref="B232">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>

--- a/customers/abas.xlsx
+++ b/customers/abas.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="230">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -706,6 +706,9 @@
   </si>
   <si>
     <t>کیک</t>
+  </si>
+  <si>
+    <t>1405/05/.20</t>
   </si>
 </sst>
 </file>
@@ -1262,7 +1265,7 @@
       </c>
       <c r="H2" s="9">
         <f>B232</f>
-        <v>2908000</v>
+        <v>2924000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4176,17 +4179,23 @@
     <row r="211" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="8">
         <f>A210+B211-C211</f>
-        <v>2908000</v>
-      </c>
-      <c r="B211" s="8"/>
+        <v>2924000</v>
+      </c>
+      <c r="B211" s="8">
+        <v>16000</v>
+      </c>
       <c r="C211" s="8"/>
-      <c r="D211" s="1"/>
-      <c r="E211" s="1"/>
+      <c r="D211" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E211" s="1" t="s">
+        <v>229</v>
+      </c>
     </row>
     <row r="212" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="8">
         <f t="shared" ref="A212:A229" si="9">A211+B212-C212</f>
-        <v>2908000</v>
+        <v>2924000</v>
       </c>
       <c r="B212" s="8"/>
       <c r="C212" s="8"/>
@@ -4196,7 +4205,7 @@
     <row r="213" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="8">
         <f t="shared" si="9"/>
-        <v>2908000</v>
+        <v>2924000</v>
       </c>
       <c r="B213" s="8"/>
       <c r="C213" s="8"/>
@@ -4206,7 +4215,7 @@
     <row r="214" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="8">
         <f t="shared" si="9"/>
-        <v>2908000</v>
+        <v>2924000</v>
       </c>
       <c r="B214" s="8"/>
       <c r="C214" s="8"/>
@@ -4216,7 +4225,7 @@
     <row r="215" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="8">
         <f t="shared" si="9"/>
-        <v>2908000</v>
+        <v>2924000</v>
       </c>
       <c r="B215" s="8"/>
       <c r="C215" s="8"/>
@@ -4226,7 +4235,7 @@
     <row r="216" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="8">
         <f t="shared" si="9"/>
-        <v>2908000</v>
+        <v>2924000</v>
       </c>
       <c r="B216" s="8"/>
       <c r="C216" s="8"/>
@@ -4236,7 +4245,7 @@
     <row r="217" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="8">
         <f t="shared" si="9"/>
-        <v>2908000</v>
+        <v>2924000</v>
       </c>
       <c r="B217" s="8"/>
       <c r="C217" s="8"/>
@@ -4246,7 +4255,7 @@
     <row r="218" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="8">
         <f t="shared" si="9"/>
-        <v>2908000</v>
+        <v>2924000</v>
       </c>
       <c r="B218" s="8"/>
       <c r="C218" s="8"/>
@@ -4256,7 +4265,7 @@
     <row r="219" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="8">
         <f t="shared" si="9"/>
-        <v>2908000</v>
+        <v>2924000</v>
       </c>
       <c r="B219" s="8"/>
       <c r="C219" s="8"/>
@@ -4266,7 +4275,7 @@
     <row r="220" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="8">
         <f t="shared" si="9"/>
-        <v>2908000</v>
+        <v>2924000</v>
       </c>
       <c r="B220" s="8"/>
       <c r="C220" s="8"/>
@@ -4276,7 +4285,7 @@
     <row r="221" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="8">
         <f t="shared" si="9"/>
-        <v>2908000</v>
+        <v>2924000</v>
       </c>
       <c r="B221" s="8"/>
       <c r="C221" s="8"/>
@@ -4286,7 +4295,7 @@
     <row r="222" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="8">
         <f t="shared" si="9"/>
-        <v>2908000</v>
+        <v>2924000</v>
       </c>
       <c r="B222" s="8"/>
       <c r="C222" s="8"/>
@@ -4296,7 +4305,7 @@
     <row r="223" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="8">
         <f t="shared" si="9"/>
-        <v>2908000</v>
+        <v>2924000</v>
       </c>
       <c r="B223" s="8"/>
       <c r="C223" s="8"/>
@@ -4306,7 +4315,7 @@
     <row r="224" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="8">
         <f t="shared" si="9"/>
-        <v>2908000</v>
+        <v>2924000</v>
       </c>
       <c r="B224" s="8"/>
       <c r="C224" s="8"/>
@@ -4316,7 +4325,7 @@
     <row r="225" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="8">
         <f t="shared" si="9"/>
-        <v>2908000</v>
+        <v>2924000</v>
       </c>
       <c r="B225" s="8"/>
       <c r="C225" s="8"/>
@@ -4326,7 +4335,7 @@
     <row r="226" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="8">
         <f t="shared" si="9"/>
-        <v>2908000</v>
+        <v>2924000</v>
       </c>
       <c r="B226" s="8"/>
       <c r="C226" s="8"/>
@@ -4336,7 +4345,7 @@
     <row r="227" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="8">
         <f t="shared" si="9"/>
-        <v>2908000</v>
+        <v>2924000</v>
       </c>
       <c r="B227" s="8"/>
       <c r="C227" s="8"/>
@@ -4346,7 +4355,7 @@
     <row r="228" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="8">
         <f t="shared" si="9"/>
-        <v>2908000</v>
+        <v>2924000</v>
       </c>
       <c r="B228" s="8"/>
       <c r="C228" s="8"/>
@@ -4356,7 +4365,7 @@
     <row r="229" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="8">
         <f t="shared" si="9"/>
-        <v>2908000</v>
+        <v>2924000</v>
       </c>
       <c r="B229" s="8"/>
       <c r="C229" s="8"/>
@@ -4366,7 +4375,7 @@
     <row r="230" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B230" s="9">
         <f>SUM(B210:B229)+B204</f>
-        <v>12106500</v>
+        <v>12122500</v>
       </c>
       <c r="C230" s="9">
         <f>SUM(C210:C229)+C204</f>
@@ -4377,7 +4386,7 @@
     <row r="232" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B232" s="10">
         <f>A229</f>
-        <v>2908000</v>
+        <v>2924000</v>
       </c>
       <c r="C232" s="12" t="s">
         <v>198</v>

--- a/customers/abas.xlsx
+++ b/customers/abas.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="232">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -709,6 +709,12 @@
   </si>
   <si>
     <t>1405/05/.20</t>
+  </si>
+  <si>
+    <t>1405/05/23</t>
+  </si>
+  <si>
+    <t>چیپس</t>
   </si>
 </sst>
 </file>
@@ -1265,7 +1271,7 @@
       </c>
       <c r="H2" s="9">
         <f>B232</f>
-        <v>2924000</v>
+        <v>2994000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4195,17 +4201,23 @@
     <row r="212" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="8">
         <f t="shared" ref="A212:A229" si="9">A211+B212-C212</f>
-        <v>2924000</v>
-      </c>
-      <c r="B212" s="8"/>
+        <v>2994000</v>
+      </c>
+      <c r="B212" s="8">
+        <v>70000</v>
+      </c>
       <c r="C212" s="8"/>
-      <c r="D212" s="1"/>
-      <c r="E212" s="1"/>
+      <c r="D212" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="E212" s="1" t="s">
+        <v>230</v>
+      </c>
     </row>
     <row r="213" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="8">
         <f t="shared" si="9"/>
-        <v>2924000</v>
+        <v>2994000</v>
       </c>
       <c r="B213" s="8"/>
       <c r="C213" s="8"/>
@@ -4215,7 +4227,7 @@
     <row r="214" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="8">
         <f t="shared" si="9"/>
-        <v>2924000</v>
+        <v>2994000</v>
       </c>
       <c r="B214" s="8"/>
       <c r="C214" s="8"/>
@@ -4225,7 +4237,7 @@
     <row r="215" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="8">
         <f t="shared" si="9"/>
-        <v>2924000</v>
+        <v>2994000</v>
       </c>
       <c r="B215" s="8"/>
       <c r="C215" s="8"/>
@@ -4235,7 +4247,7 @@
     <row r="216" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="8">
         <f t="shared" si="9"/>
-        <v>2924000</v>
+        <v>2994000</v>
       </c>
       <c r="B216" s="8"/>
       <c r="C216" s="8"/>
@@ -4245,7 +4257,7 @@
     <row r="217" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="8">
         <f t="shared" si="9"/>
-        <v>2924000</v>
+        <v>2994000</v>
       </c>
       <c r="B217" s="8"/>
       <c r="C217" s="8"/>
@@ -4255,7 +4267,7 @@
     <row r="218" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="8">
         <f t="shared" si="9"/>
-        <v>2924000</v>
+        <v>2994000</v>
       </c>
       <c r="B218" s="8"/>
       <c r="C218" s="8"/>
@@ -4265,7 +4277,7 @@
     <row r="219" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="8">
         <f t="shared" si="9"/>
-        <v>2924000</v>
+        <v>2994000</v>
       </c>
       <c r="B219" s="8"/>
       <c r="C219" s="8"/>
@@ -4275,7 +4287,7 @@
     <row r="220" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="8">
         <f t="shared" si="9"/>
-        <v>2924000</v>
+        <v>2994000</v>
       </c>
       <c r="B220" s="8"/>
       <c r="C220" s="8"/>
@@ -4285,7 +4297,7 @@
     <row r="221" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="8">
         <f t="shared" si="9"/>
-        <v>2924000</v>
+        <v>2994000</v>
       </c>
       <c r="B221" s="8"/>
       <c r="C221" s="8"/>
@@ -4295,7 +4307,7 @@
     <row r="222" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="8">
         <f t="shared" si="9"/>
-        <v>2924000</v>
+        <v>2994000</v>
       </c>
       <c r="B222" s="8"/>
       <c r="C222" s="8"/>
@@ -4305,7 +4317,7 @@
     <row r="223" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="8">
         <f t="shared" si="9"/>
-        <v>2924000</v>
+        <v>2994000</v>
       </c>
       <c r="B223" s="8"/>
       <c r="C223" s="8"/>
@@ -4315,7 +4327,7 @@
     <row r="224" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="8">
         <f t="shared" si="9"/>
-        <v>2924000</v>
+        <v>2994000</v>
       </c>
       <c r="B224" s="8"/>
       <c r="C224" s="8"/>
@@ -4325,7 +4337,7 @@
     <row r="225" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="8">
         <f t="shared" si="9"/>
-        <v>2924000</v>
+        <v>2994000</v>
       </c>
       <c r="B225" s="8"/>
       <c r="C225" s="8"/>
@@ -4335,7 +4347,7 @@
     <row r="226" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="8">
         <f t="shared" si="9"/>
-        <v>2924000</v>
+        <v>2994000</v>
       </c>
       <c r="B226" s="8"/>
       <c r="C226" s="8"/>
@@ -4345,7 +4357,7 @@
     <row r="227" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="8">
         <f t="shared" si="9"/>
-        <v>2924000</v>
+        <v>2994000</v>
       </c>
       <c r="B227" s="8"/>
       <c r="C227" s="8"/>
@@ -4355,7 +4367,7 @@
     <row r="228" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="8">
         <f t="shared" si="9"/>
-        <v>2924000</v>
+        <v>2994000</v>
       </c>
       <c r="B228" s="8"/>
       <c r="C228" s="8"/>
@@ -4365,7 +4377,7 @@
     <row r="229" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="8">
         <f t="shared" si="9"/>
-        <v>2924000</v>
+        <v>2994000</v>
       </c>
       <c r="B229" s="8"/>
       <c r="C229" s="8"/>
@@ -4375,7 +4387,7 @@
     <row r="230" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B230" s="9">
         <f>SUM(B210:B229)+B204</f>
-        <v>12122500</v>
+        <v>12192500</v>
       </c>
       <c r="C230" s="9">
         <f>SUM(C210:C229)+C204</f>
@@ -4386,7 +4398,7 @@
     <row r="232" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B232" s="10">
         <f>A229</f>
-        <v>2924000</v>
+        <v>2994000</v>
       </c>
       <c r="C232" s="12" t="s">
         <v>198</v>

--- a/customers/abas.xlsx
+++ b/customers/abas.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="232">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="H2" s="9">
         <f>B232</f>
-        <v>2994000</v>
+        <v>3044000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4217,17 +4217,21 @@
     <row r="213" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="8">
         <f t="shared" si="9"/>
-        <v>2994000</v>
-      </c>
-      <c r="B213" s="8"/>
+        <v>3044000</v>
+      </c>
+      <c r="B213" s="8">
+        <v>50000</v>
+      </c>
       <c r="C213" s="8"/>
-      <c r="D213" s="1"/>
+      <c r="D213" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="E213" s="1"/>
     </row>
     <row r="214" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="8">
         <f t="shared" si="9"/>
-        <v>2994000</v>
+        <v>3044000</v>
       </c>
       <c r="B214" s="8"/>
       <c r="C214" s="8"/>
@@ -4237,7 +4241,7 @@
     <row r="215" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="8">
         <f t="shared" si="9"/>
-        <v>2994000</v>
+        <v>3044000</v>
       </c>
       <c r="B215" s="8"/>
       <c r="C215" s="8"/>
@@ -4247,7 +4251,7 @@
     <row r="216" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="8">
         <f t="shared" si="9"/>
-        <v>2994000</v>
+        <v>3044000</v>
       </c>
       <c r="B216" s="8"/>
       <c r="C216" s="8"/>
@@ -4257,7 +4261,7 @@
     <row r="217" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="8">
         <f t="shared" si="9"/>
-        <v>2994000</v>
+        <v>3044000</v>
       </c>
       <c r="B217" s="8"/>
       <c r="C217" s="8"/>
@@ -4267,7 +4271,7 @@
     <row r="218" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="8">
         <f t="shared" si="9"/>
-        <v>2994000</v>
+        <v>3044000</v>
       </c>
       <c r="B218" s="8"/>
       <c r="C218" s="8"/>
@@ -4277,7 +4281,7 @@
     <row r="219" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="8">
         <f t="shared" si="9"/>
-        <v>2994000</v>
+        <v>3044000</v>
       </c>
       <c r="B219" s="8"/>
       <c r="C219" s="8"/>
@@ -4287,7 +4291,7 @@
     <row r="220" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="8">
         <f t="shared" si="9"/>
-        <v>2994000</v>
+        <v>3044000</v>
       </c>
       <c r="B220" s="8"/>
       <c r="C220" s="8"/>
@@ -4297,7 +4301,7 @@
     <row r="221" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="8">
         <f t="shared" si="9"/>
-        <v>2994000</v>
+        <v>3044000</v>
       </c>
       <c r="B221" s="8"/>
       <c r="C221" s="8"/>
@@ -4307,7 +4311,7 @@
     <row r="222" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="8">
         <f t="shared" si="9"/>
-        <v>2994000</v>
+        <v>3044000</v>
       </c>
       <c r="B222" s="8"/>
       <c r="C222" s="8"/>
@@ -4317,7 +4321,7 @@
     <row r="223" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="8">
         <f t="shared" si="9"/>
-        <v>2994000</v>
+        <v>3044000</v>
       </c>
       <c r="B223" s="8"/>
       <c r="C223" s="8"/>
@@ -4327,7 +4331,7 @@
     <row r="224" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="8">
         <f t="shared" si="9"/>
-        <v>2994000</v>
+        <v>3044000</v>
       </c>
       <c r="B224" s="8"/>
       <c r="C224" s="8"/>
@@ -4337,7 +4341,7 @@
     <row r="225" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="8">
         <f t="shared" si="9"/>
-        <v>2994000</v>
+        <v>3044000</v>
       </c>
       <c r="B225" s="8"/>
       <c r="C225" s="8"/>
@@ -4347,7 +4351,7 @@
     <row r="226" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="8">
         <f t="shared" si="9"/>
-        <v>2994000</v>
+        <v>3044000</v>
       </c>
       <c r="B226" s="8"/>
       <c r="C226" s="8"/>
@@ -4357,7 +4361,7 @@
     <row r="227" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="8">
         <f t="shared" si="9"/>
-        <v>2994000</v>
+        <v>3044000</v>
       </c>
       <c r="B227" s="8"/>
       <c r="C227" s="8"/>
@@ -4367,7 +4371,7 @@
     <row r="228" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="8">
         <f t="shared" si="9"/>
-        <v>2994000</v>
+        <v>3044000</v>
       </c>
       <c r="B228" s="8"/>
       <c r="C228" s="8"/>
@@ -4377,7 +4381,7 @@
     <row r="229" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="8">
         <f t="shared" si="9"/>
-        <v>2994000</v>
+        <v>3044000</v>
       </c>
       <c r="B229" s="8"/>
       <c r="C229" s="8"/>
@@ -4387,7 +4391,7 @@
     <row r="230" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B230" s="9">
         <f>SUM(B210:B229)+B204</f>
-        <v>12192500</v>
+        <v>12242500</v>
       </c>
       <c r="C230" s="9">
         <f>SUM(C210:C229)+C204</f>
@@ -4398,7 +4402,7 @@
     <row r="232" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B232" s="10">
         <f>A229</f>
-        <v>2994000</v>
+        <v>3044000</v>
       </c>
       <c r="C232" s="12" t="s">
         <v>198</v>

--- a/customers/abas.xlsx
+++ b/customers/abas.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="233">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -715,6 +715,9 @@
   </si>
   <si>
     <t>چیپس</t>
+  </si>
+  <si>
+    <t>سیگار مغز</t>
   </si>
 </sst>
 </file>
@@ -1271,7 +1274,7 @@
       </c>
       <c r="H2" s="9">
         <f>B232</f>
-        <v>3044000</v>
+        <v>3292000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4231,27 +4234,37 @@
     <row r="214" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="8">
         <f t="shared" si="9"/>
-        <v>3044000</v>
-      </c>
-      <c r="B214" s="8"/>
+        <v>3206000</v>
+      </c>
+      <c r="B214" s="8">
+        <v>162000</v>
+      </c>
       <c r="C214" s="8"/>
-      <c r="D214" s="1"/>
-      <c r="E214" s="1"/>
+      <c r="D214" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E214" s="1" t="s">
+        <v>230</v>
+      </c>
     </row>
     <row r="215" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="8">
         <f t="shared" si="9"/>
-        <v>3044000</v>
-      </c>
-      <c r="B215" s="8"/>
+        <v>3292000</v>
+      </c>
+      <c r="B215" s="8">
+        <v>86000</v>
+      </c>
       <c r="C215" s="8"/>
-      <c r="D215" s="1"/>
+      <c r="D215" s="1" t="s">
+        <v>232</v>
+      </c>
       <c r="E215" s="1"/>
     </row>
     <row r="216" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="8">
         <f t="shared" si="9"/>
-        <v>3044000</v>
+        <v>3292000</v>
       </c>
       <c r="B216" s="8"/>
       <c r="C216" s="8"/>
@@ -4261,7 +4274,7 @@
     <row r="217" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="8">
         <f t="shared" si="9"/>
-        <v>3044000</v>
+        <v>3292000</v>
       </c>
       <c r="B217" s="8"/>
       <c r="C217" s="8"/>
@@ -4271,7 +4284,7 @@
     <row r="218" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="8">
         <f t="shared" si="9"/>
-        <v>3044000</v>
+        <v>3292000</v>
       </c>
       <c r="B218" s="8"/>
       <c r="C218" s="8"/>
@@ -4281,7 +4294,7 @@
     <row r="219" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="8">
         <f t="shared" si="9"/>
-        <v>3044000</v>
+        <v>3292000</v>
       </c>
       <c r="B219" s="8"/>
       <c r="C219" s="8"/>
@@ -4291,7 +4304,7 @@
     <row r="220" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="8">
         <f t="shared" si="9"/>
-        <v>3044000</v>
+        <v>3292000</v>
       </c>
       <c r="B220" s="8"/>
       <c r="C220" s="8"/>
@@ -4301,7 +4314,7 @@
     <row r="221" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="8">
         <f t="shared" si="9"/>
-        <v>3044000</v>
+        <v>3292000</v>
       </c>
       <c r="B221" s="8"/>
       <c r="C221" s="8"/>
@@ -4311,7 +4324,7 @@
     <row r="222" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="8">
         <f t="shared" si="9"/>
-        <v>3044000</v>
+        <v>3292000</v>
       </c>
       <c r="B222" s="8"/>
       <c r="C222" s="8"/>
@@ -4321,7 +4334,7 @@
     <row r="223" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="8">
         <f t="shared" si="9"/>
-        <v>3044000</v>
+        <v>3292000</v>
       </c>
       <c r="B223" s="8"/>
       <c r="C223" s="8"/>
@@ -4331,7 +4344,7 @@
     <row r="224" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="8">
         <f t="shared" si="9"/>
-        <v>3044000</v>
+        <v>3292000</v>
       </c>
       <c r="B224" s="8"/>
       <c r="C224" s="8"/>
@@ -4341,7 +4354,7 @@
     <row r="225" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="8">
         <f t="shared" si="9"/>
-        <v>3044000</v>
+        <v>3292000</v>
       </c>
       <c r="B225" s="8"/>
       <c r="C225" s="8"/>
@@ -4351,7 +4364,7 @@
     <row r="226" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="8">
         <f t="shared" si="9"/>
-        <v>3044000</v>
+        <v>3292000</v>
       </c>
       <c r="B226" s="8"/>
       <c r="C226" s="8"/>
@@ -4361,7 +4374,7 @@
     <row r="227" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="8">
         <f t="shared" si="9"/>
-        <v>3044000</v>
+        <v>3292000</v>
       </c>
       <c r="B227" s="8"/>
       <c r="C227" s="8"/>
@@ -4371,7 +4384,7 @@
     <row r="228" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="8">
         <f t="shared" si="9"/>
-        <v>3044000</v>
+        <v>3292000</v>
       </c>
       <c r="B228" s="8"/>
       <c r="C228" s="8"/>
@@ -4381,7 +4394,7 @@
     <row r="229" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="8">
         <f t="shared" si="9"/>
-        <v>3044000</v>
+        <v>3292000</v>
       </c>
       <c r="B229" s="8"/>
       <c r="C229" s="8"/>
@@ -4391,7 +4404,7 @@
     <row r="230" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B230" s="9">
         <f>SUM(B210:B229)+B204</f>
-        <v>12242500</v>
+        <v>12490500</v>
       </c>
       <c r="C230" s="9">
         <f>SUM(C210:C229)+C204</f>
@@ -4402,7 +4415,7 @@
     <row r="232" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B232" s="10">
         <f>A229</f>
-        <v>3044000</v>
+        <v>3292000</v>
       </c>
       <c r="C232" s="12" t="s">
         <v>198</v>

--- a/customers/abas.xlsx
+++ b/customers/abas.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="234">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -718,6 +718,9 @@
   </si>
   <si>
     <t>سیگار مغز</t>
+  </si>
+  <si>
+    <t>1405/05/24</t>
   </si>
 </sst>
 </file>
@@ -4244,7 +4247,7 @@
         <v>143</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
     <row r="215" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">

--- a/customers/abas.xlsx
+++ b/customers/abas.xlsx
@@ -1277,7 +1277,7 @@
       </c>
       <c r="H2" s="9">
         <f>B232</f>
-        <v>3292000</v>
+        <v>3292500</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4267,9 +4267,11 @@
     <row r="216" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="8">
         <f t="shared" si="9"/>
-        <v>3292000</v>
-      </c>
-      <c r="B216" s="8"/>
+        <v>3292500</v>
+      </c>
+      <c r="B216" s="8">
+        <v>500</v>
+      </c>
       <c r="C216" s="8"/>
       <c r="D216" s="1"/>
       <c r="E216" s="1"/>
@@ -4277,7 +4279,7 @@
     <row r="217" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="8">
         <f t="shared" si="9"/>
-        <v>3292000</v>
+        <v>3292500</v>
       </c>
       <c r="B217" s="8"/>
       <c r="C217" s="8"/>
@@ -4287,7 +4289,7 @@
     <row r="218" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="8">
         <f t="shared" si="9"/>
-        <v>3292000</v>
+        <v>3292500</v>
       </c>
       <c r="B218" s="8"/>
       <c r="C218" s="8"/>
@@ -4297,7 +4299,7 @@
     <row r="219" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="8">
         <f t="shared" si="9"/>
-        <v>3292000</v>
+        <v>3292500</v>
       </c>
       <c r="B219" s="8"/>
       <c r="C219" s="8"/>
@@ -4307,7 +4309,7 @@
     <row r="220" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="8">
         <f t="shared" si="9"/>
-        <v>3292000</v>
+        <v>3292500</v>
       </c>
       <c r="B220" s="8"/>
       <c r="C220" s="8"/>
@@ -4317,7 +4319,7 @@
     <row r="221" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="8">
         <f t="shared" si="9"/>
-        <v>3292000</v>
+        <v>3292500</v>
       </c>
       <c r="B221" s="8"/>
       <c r="C221" s="8"/>
@@ -4327,7 +4329,7 @@
     <row r="222" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="8">
         <f t="shared" si="9"/>
-        <v>3292000</v>
+        <v>3292500</v>
       </c>
       <c r="B222" s="8"/>
       <c r="C222" s="8"/>
@@ -4337,7 +4339,7 @@
     <row r="223" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="8">
         <f t="shared" si="9"/>
-        <v>3292000</v>
+        <v>3292500</v>
       </c>
       <c r="B223" s="8"/>
       <c r="C223" s="8"/>
@@ -4347,7 +4349,7 @@
     <row r="224" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="8">
         <f t="shared" si="9"/>
-        <v>3292000</v>
+        <v>3292500</v>
       </c>
       <c r="B224" s="8"/>
       <c r="C224" s="8"/>
@@ -4357,7 +4359,7 @@
     <row r="225" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="8">
         <f t="shared" si="9"/>
-        <v>3292000</v>
+        <v>3292500</v>
       </c>
       <c r="B225" s="8"/>
       <c r="C225" s="8"/>
@@ -4367,7 +4369,7 @@
     <row r="226" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="8">
         <f t="shared" si="9"/>
-        <v>3292000</v>
+        <v>3292500</v>
       </c>
       <c r="B226" s="8"/>
       <c r="C226" s="8"/>
@@ -4377,7 +4379,7 @@
     <row r="227" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="8">
         <f t="shared" si="9"/>
-        <v>3292000</v>
+        <v>3292500</v>
       </c>
       <c r="B227" s="8"/>
       <c r="C227" s="8"/>
@@ -4387,7 +4389,7 @@
     <row r="228" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="8">
         <f t="shared" si="9"/>
-        <v>3292000</v>
+        <v>3292500</v>
       </c>
       <c r="B228" s="8"/>
       <c r="C228" s="8"/>
@@ -4397,7 +4399,7 @@
     <row r="229" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="8">
         <f t="shared" si="9"/>
-        <v>3292000</v>
+        <v>3292500</v>
       </c>
       <c r="B229" s="8"/>
       <c r="C229" s="8"/>
@@ -4407,7 +4409,7 @@
     <row r="230" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B230" s="9">
         <f>SUM(B210:B229)+B204</f>
-        <v>12490500</v>
+        <v>12491000</v>
       </c>
       <c r="C230" s="9">
         <f>SUM(C210:C229)+C204</f>
@@ -4418,7 +4420,7 @@
     <row r="232" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B232" s="10">
         <f>A229</f>
-        <v>3292000</v>
+        <v>3292500</v>
       </c>
       <c r="C232" s="12" t="s">
         <v>198</v>

--- a/customers/abas.xlsx
+++ b/customers/abas.xlsx
@@ -1277,7 +1277,7 @@
       </c>
       <c r="H2" s="9">
         <f>B232</f>
-        <v>3292500</v>
+        <v>3292000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4267,11 +4267,9 @@
     <row r="216" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="8">
         <f t="shared" si="9"/>
-        <v>3292500</v>
-      </c>
-      <c r="B216" s="8">
-        <v>500</v>
-      </c>
+        <v>3292000</v>
+      </c>
+      <c r="B216" s="8"/>
       <c r="C216" s="8"/>
       <c r="D216" s="1"/>
       <c r="E216" s="1"/>
@@ -4279,7 +4277,7 @@
     <row r="217" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="8">
         <f t="shared" si="9"/>
-        <v>3292500</v>
+        <v>3292000</v>
       </c>
       <c r="B217" s="8"/>
       <c r="C217" s="8"/>
@@ -4289,7 +4287,7 @@
     <row r="218" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="8">
         <f t="shared" si="9"/>
-        <v>3292500</v>
+        <v>3292000</v>
       </c>
       <c r="B218" s="8"/>
       <c r="C218" s="8"/>
@@ -4299,7 +4297,7 @@
     <row r="219" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="8">
         <f t="shared" si="9"/>
-        <v>3292500</v>
+        <v>3292000</v>
       </c>
       <c r="B219" s="8"/>
       <c r="C219" s="8"/>
@@ -4309,7 +4307,7 @@
     <row r="220" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="8">
         <f t="shared" si="9"/>
-        <v>3292500</v>
+        <v>3292000</v>
       </c>
       <c r="B220" s="8"/>
       <c r="C220" s="8"/>
@@ -4319,7 +4317,7 @@
     <row r="221" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="8">
         <f t="shared" si="9"/>
-        <v>3292500</v>
+        <v>3292000</v>
       </c>
       <c r="B221" s="8"/>
       <c r="C221" s="8"/>
@@ -4329,7 +4327,7 @@
     <row r="222" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="8">
         <f t="shared" si="9"/>
-        <v>3292500</v>
+        <v>3292000</v>
       </c>
       <c r="B222" s="8"/>
       <c r="C222" s="8"/>
@@ -4339,7 +4337,7 @@
     <row r="223" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="8">
         <f t="shared" si="9"/>
-        <v>3292500</v>
+        <v>3292000</v>
       </c>
       <c r="B223" s="8"/>
       <c r="C223" s="8"/>
@@ -4349,7 +4347,7 @@
     <row r="224" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="8">
         <f t="shared" si="9"/>
-        <v>3292500</v>
+        <v>3292000</v>
       </c>
       <c r="B224" s="8"/>
       <c r="C224" s="8"/>
@@ -4359,7 +4357,7 @@
     <row r="225" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="8">
         <f t="shared" si="9"/>
-        <v>3292500</v>
+        <v>3292000</v>
       </c>
       <c r="B225" s="8"/>
       <c r="C225" s="8"/>
@@ -4369,7 +4367,7 @@
     <row r="226" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="8">
         <f t="shared" si="9"/>
-        <v>3292500</v>
+        <v>3292000</v>
       </c>
       <c r="B226" s="8"/>
       <c r="C226" s="8"/>
@@ -4379,7 +4377,7 @@
     <row r="227" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="8">
         <f t="shared" si="9"/>
-        <v>3292500</v>
+        <v>3292000</v>
       </c>
       <c r="B227" s="8"/>
       <c r="C227" s="8"/>
@@ -4389,7 +4387,7 @@
     <row r="228" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="8">
         <f t="shared" si="9"/>
-        <v>3292500</v>
+        <v>3292000</v>
       </c>
       <c r="B228" s="8"/>
       <c r="C228" s="8"/>
@@ -4399,7 +4397,7 @@
     <row r="229" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="8">
         <f t="shared" si="9"/>
-        <v>3292500</v>
+        <v>3292000</v>
       </c>
       <c r="B229" s="8"/>
       <c r="C229" s="8"/>
@@ -4409,7 +4407,7 @@
     <row r="230" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B230" s="9">
         <f>SUM(B210:B229)+B204</f>
-        <v>12491000</v>
+        <v>12490500</v>
       </c>
       <c r="C230" s="9">
         <f>SUM(C210:C229)+C204</f>
@@ -4420,7 +4418,7 @@
     <row r="232" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B232" s="10">
         <f>A229</f>
-        <v>3292500</v>
+        <v>3292000</v>
       </c>
       <c r="C232" s="12" t="s">
         <v>198</v>

--- a/customers/abas.xlsx
+++ b/customers/abas.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="235">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -721,6 +721,9 @@
   </si>
   <si>
     <t>1405/05/24</t>
+  </si>
+  <si>
+    <t>1405/05/31</t>
   </si>
 </sst>
 </file>
@@ -1277,7 +1280,7 @@
       </c>
       <c r="H2" s="9">
         <f>B232</f>
-        <v>3292000</v>
+        <v>3317000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4267,17 +4270,23 @@
     <row r="216" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="8">
         <f t="shared" si="9"/>
-        <v>3292000</v>
-      </c>
-      <c r="B216" s="8"/>
+        <v>3317000</v>
+      </c>
+      <c r="B216" s="8">
+        <v>25000</v>
+      </c>
       <c r="C216" s="8"/>
-      <c r="D216" s="1"/>
-      <c r="E216" s="1"/>
+      <c r="D216" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="E216" s="1" t="s">
+        <v>234</v>
+      </c>
     </row>
     <row r="217" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="8">
         <f t="shared" si="9"/>
-        <v>3292000</v>
+        <v>3317000</v>
       </c>
       <c r="B217" s="8"/>
       <c r="C217" s="8"/>
@@ -4287,7 +4296,7 @@
     <row r="218" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="8">
         <f t="shared" si="9"/>
-        <v>3292000</v>
+        <v>3317000</v>
       </c>
       <c r="B218" s="8"/>
       <c r="C218" s="8"/>
@@ -4297,7 +4306,7 @@
     <row r="219" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="8">
         <f t="shared" si="9"/>
-        <v>3292000</v>
+        <v>3317000</v>
       </c>
       <c r="B219" s="8"/>
       <c r="C219" s="8"/>
@@ -4307,7 +4316,7 @@
     <row r="220" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="8">
         <f t="shared" si="9"/>
-        <v>3292000</v>
+        <v>3317000</v>
       </c>
       <c r="B220" s="8"/>
       <c r="C220" s="8"/>
@@ -4317,7 +4326,7 @@
     <row r="221" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="8">
         <f t="shared" si="9"/>
-        <v>3292000</v>
+        <v>3317000</v>
       </c>
       <c r="B221" s="8"/>
       <c r="C221" s="8"/>
@@ -4327,7 +4336,7 @@
     <row r="222" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="8">
         <f t="shared" si="9"/>
-        <v>3292000</v>
+        <v>3317000</v>
       </c>
       <c r="B222" s="8"/>
       <c r="C222" s="8"/>
@@ -4337,7 +4346,7 @@
     <row r="223" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="8">
         <f t="shared" si="9"/>
-        <v>3292000</v>
+        <v>3317000</v>
       </c>
       <c r="B223" s="8"/>
       <c r="C223" s="8"/>
@@ -4347,7 +4356,7 @@
     <row r="224" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="8">
         <f t="shared" si="9"/>
-        <v>3292000</v>
+        <v>3317000</v>
       </c>
       <c r="B224" s="8"/>
       <c r="C224" s="8"/>
@@ -4357,7 +4366,7 @@
     <row r="225" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="8">
         <f t="shared" si="9"/>
-        <v>3292000</v>
+        <v>3317000</v>
       </c>
       <c r="B225" s="8"/>
       <c r="C225" s="8"/>
@@ -4367,7 +4376,7 @@
     <row r="226" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="8">
         <f t="shared" si="9"/>
-        <v>3292000</v>
+        <v>3317000</v>
       </c>
       <c r="B226" s="8"/>
       <c r="C226" s="8"/>
@@ -4377,7 +4386,7 @@
     <row r="227" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="8">
         <f t="shared" si="9"/>
-        <v>3292000</v>
+        <v>3317000</v>
       </c>
       <c r="B227" s="8"/>
       <c r="C227" s="8"/>
@@ -4387,7 +4396,7 @@
     <row r="228" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="8">
         <f t="shared" si="9"/>
-        <v>3292000</v>
+        <v>3317000</v>
       </c>
       <c r="B228" s="8"/>
       <c r="C228" s="8"/>
@@ -4397,7 +4406,7 @@
     <row r="229" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="8">
         <f t="shared" si="9"/>
-        <v>3292000</v>
+        <v>3317000</v>
       </c>
       <c r="B229" s="8"/>
       <c r="C229" s="8"/>
@@ -4407,7 +4416,7 @@
     <row r="230" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B230" s="9">
         <f>SUM(B210:B229)+B204</f>
-        <v>12490500</v>
+        <v>12515500</v>
       </c>
       <c r="C230" s="9">
         <f>SUM(C210:C229)+C204</f>
@@ -4418,7 +4427,7 @@
     <row r="232" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B232" s="10">
         <f>A229</f>
-        <v>3292000</v>
+        <v>3317000</v>
       </c>
       <c r="C232" s="12" t="s">
         <v>198</v>

--- a/customers/abas.xlsx
+++ b/customers/abas.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="236">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -724,6 +724,9 @@
   </si>
   <si>
     <t>1405/05/31</t>
+  </si>
+  <si>
+    <t>1405/06/01</t>
   </si>
 </sst>
 </file>
@@ -1280,7 +1283,7 @@
       </c>
       <c r="H2" s="9">
         <f>B232</f>
-        <v>3317000</v>
+        <v>3388000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4286,17 +4289,23 @@
     <row r="217" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="8">
         <f t="shared" si="9"/>
-        <v>3317000</v>
-      </c>
-      <c r="B217" s="8"/>
+        <v>3388000</v>
+      </c>
+      <c r="B217" s="8">
+        <v>71000</v>
+      </c>
       <c r="C217" s="8"/>
-      <c r="D217" s="1"/>
-      <c r="E217" s="1"/>
+      <c r="D217" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="E217" s="1" t="s">
+        <v>235</v>
+      </c>
     </row>
     <row r="218" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="8">
         <f t="shared" si="9"/>
-        <v>3317000</v>
+        <v>3388000</v>
       </c>
       <c r="B218" s="8"/>
       <c r="C218" s="8"/>
@@ -4306,7 +4315,7 @@
     <row r="219" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="8">
         <f t="shared" si="9"/>
-        <v>3317000</v>
+        <v>3388000</v>
       </c>
       <c r="B219" s="8"/>
       <c r="C219" s="8"/>
@@ -4316,7 +4325,7 @@
     <row r="220" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="8">
         <f t="shared" si="9"/>
-        <v>3317000</v>
+        <v>3388000</v>
       </c>
       <c r="B220" s="8"/>
       <c r="C220" s="8"/>
@@ -4326,7 +4335,7 @@
     <row r="221" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="8">
         <f t="shared" si="9"/>
-        <v>3317000</v>
+        <v>3388000</v>
       </c>
       <c r="B221" s="8"/>
       <c r="C221" s="8"/>
@@ -4336,7 +4345,7 @@
     <row r="222" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="8">
         <f t="shared" si="9"/>
-        <v>3317000</v>
+        <v>3388000</v>
       </c>
       <c r="B222" s="8"/>
       <c r="C222" s="8"/>
@@ -4346,7 +4355,7 @@
     <row r="223" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="8">
         <f t="shared" si="9"/>
-        <v>3317000</v>
+        <v>3388000</v>
       </c>
       <c r="B223" s="8"/>
       <c r="C223" s="8"/>
@@ -4356,7 +4365,7 @@
     <row r="224" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="8">
         <f t="shared" si="9"/>
-        <v>3317000</v>
+        <v>3388000</v>
       </c>
       <c r="B224" s="8"/>
       <c r="C224" s="8"/>
@@ -4366,7 +4375,7 @@
     <row r="225" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="8">
         <f t="shared" si="9"/>
-        <v>3317000</v>
+        <v>3388000</v>
       </c>
       <c r="B225" s="8"/>
       <c r="C225" s="8"/>
@@ -4376,7 +4385,7 @@
     <row r="226" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="8">
         <f t="shared" si="9"/>
-        <v>3317000</v>
+        <v>3388000</v>
       </c>
       <c r="B226" s="8"/>
       <c r="C226" s="8"/>
@@ -4386,7 +4395,7 @@
     <row r="227" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="8">
         <f t="shared" si="9"/>
-        <v>3317000</v>
+        <v>3388000</v>
       </c>
       <c r="B227" s="8"/>
       <c r="C227" s="8"/>
@@ -4396,7 +4405,7 @@
     <row r="228" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="8">
         <f t="shared" si="9"/>
-        <v>3317000</v>
+        <v>3388000</v>
       </c>
       <c r="B228" s="8"/>
       <c r="C228" s="8"/>
@@ -4406,7 +4415,7 @@
     <row r="229" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="8">
         <f t="shared" si="9"/>
-        <v>3317000</v>
+        <v>3388000</v>
       </c>
       <c r="B229" s="8"/>
       <c r="C229" s="8"/>
@@ -4416,7 +4425,7 @@
     <row r="230" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B230" s="9">
         <f>SUM(B210:B229)+B204</f>
-        <v>12515500</v>
+        <v>12586500</v>
       </c>
       <c r="C230" s="9">
         <f>SUM(C210:C229)+C204</f>
@@ -4427,7 +4436,7 @@
     <row r="232" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B232" s="10">
         <f>A229</f>
-        <v>3317000</v>
+        <v>3388000</v>
       </c>
       <c r="C232" s="12" t="s">
         <v>198</v>

--- a/customers/abas.xlsx
+++ b/customers/abas.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="237">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -727,6 +727,9 @@
   </si>
   <si>
     <t>1405/06/01</t>
+  </si>
+  <si>
+    <t>1405/06/02</t>
   </si>
 </sst>
 </file>
@@ -1283,7 +1286,7 @@
       </c>
       <c r="H2" s="9">
         <f>B232</f>
-        <v>3388000</v>
+        <v>3577000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4305,17 +4308,23 @@
     <row r="218" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="8">
         <f t="shared" si="9"/>
-        <v>3388000</v>
-      </c>
-      <c r="B218" s="8"/>
+        <v>3577000</v>
+      </c>
+      <c r="B218" s="8">
+        <v>189000</v>
+      </c>
       <c r="C218" s="8"/>
-      <c r="D218" s="1"/>
-      <c r="E218" s="1"/>
+      <c r="D218" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E218" s="1" t="s">
+        <v>236</v>
+      </c>
     </row>
     <row r="219" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="8">
         <f t="shared" si="9"/>
-        <v>3388000</v>
+        <v>3577000</v>
       </c>
       <c r="B219" s="8"/>
       <c r="C219" s="8"/>
@@ -4325,7 +4334,7 @@
     <row r="220" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="8">
         <f t="shared" si="9"/>
-        <v>3388000</v>
+        <v>3577000</v>
       </c>
       <c r="B220" s="8"/>
       <c r="C220" s="8"/>
@@ -4335,7 +4344,7 @@
     <row r="221" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="8">
         <f t="shared" si="9"/>
-        <v>3388000</v>
+        <v>3577000</v>
       </c>
       <c r="B221" s="8"/>
       <c r="C221" s="8"/>
@@ -4345,7 +4354,7 @@
     <row r="222" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="8">
         <f t="shared" si="9"/>
-        <v>3388000</v>
+        <v>3577000</v>
       </c>
       <c r="B222" s="8"/>
       <c r="C222" s="8"/>
@@ -4355,7 +4364,7 @@
     <row r="223" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="8">
         <f t="shared" si="9"/>
-        <v>3388000</v>
+        <v>3577000</v>
       </c>
       <c r="B223" s="8"/>
       <c r="C223" s="8"/>
@@ -4365,7 +4374,7 @@
     <row r="224" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="8">
         <f t="shared" si="9"/>
-        <v>3388000</v>
+        <v>3577000</v>
       </c>
       <c r="B224" s="8"/>
       <c r="C224" s="8"/>
@@ -4375,7 +4384,7 @@
     <row r="225" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="8">
         <f t="shared" si="9"/>
-        <v>3388000</v>
+        <v>3577000</v>
       </c>
       <c r="B225" s="8"/>
       <c r="C225" s="8"/>
@@ -4385,7 +4394,7 @@
     <row r="226" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="8">
         <f t="shared" si="9"/>
-        <v>3388000</v>
+        <v>3577000</v>
       </c>
       <c r="B226" s="8"/>
       <c r="C226" s="8"/>
@@ -4395,7 +4404,7 @@
     <row r="227" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="8">
         <f t="shared" si="9"/>
-        <v>3388000</v>
+        <v>3577000</v>
       </c>
       <c r="B227" s="8"/>
       <c r="C227" s="8"/>
@@ -4405,7 +4414,7 @@
     <row r="228" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="8">
         <f t="shared" si="9"/>
-        <v>3388000</v>
+        <v>3577000</v>
       </c>
       <c r="B228" s="8"/>
       <c r="C228" s="8"/>
@@ -4415,7 +4424,7 @@
     <row r="229" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="8">
         <f t="shared" si="9"/>
-        <v>3388000</v>
+        <v>3577000</v>
       </c>
       <c r="B229" s="8"/>
       <c r="C229" s="8"/>
@@ -4425,7 +4434,7 @@
     <row r="230" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B230" s="9">
         <f>SUM(B210:B229)+B204</f>
-        <v>12586500</v>
+        <v>12775500</v>
       </c>
       <c r="C230" s="9">
         <f>SUM(C210:C229)+C204</f>
@@ -4436,7 +4445,7 @@
     <row r="232" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B232" s="10">
         <f>A229</f>
-        <v>3388000</v>
+        <v>3577000</v>
       </c>
       <c r="C232" s="12" t="s">
         <v>198</v>

--- a/customers/abas.xlsx
+++ b/customers/abas.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="239">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -730,6 +730,12 @@
   </si>
   <si>
     <t>1405/06/02</t>
+  </si>
+  <si>
+    <t>1405/06/05</t>
+  </si>
+  <si>
+    <t>اوسکار</t>
   </si>
 </sst>
 </file>
@@ -1286,7 +1292,7 @@
       </c>
       <c r="H2" s="9">
         <f>B232</f>
-        <v>3577000</v>
+        <v>3677000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4324,17 +4330,23 @@
     <row r="219" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="8">
         <f t="shared" si="9"/>
-        <v>3577000</v>
-      </c>
-      <c r="B219" s="8"/>
+        <v>3677000</v>
+      </c>
+      <c r="B219" s="8">
+        <v>100000</v>
+      </c>
       <c r="C219" s="8"/>
-      <c r="D219" s="1"/>
-      <c r="E219" s="1"/>
+      <c r="D219" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="E219" s="1" t="s">
+        <v>237</v>
+      </c>
     </row>
     <row r="220" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="8">
         <f t="shared" si="9"/>
-        <v>3577000</v>
+        <v>3677000</v>
       </c>
       <c r="B220" s="8"/>
       <c r="C220" s="8"/>
@@ -4344,7 +4356,7 @@
     <row r="221" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="8">
         <f t="shared" si="9"/>
-        <v>3577000</v>
+        <v>3677000</v>
       </c>
       <c r="B221" s="8"/>
       <c r="C221" s="8"/>
@@ -4354,7 +4366,7 @@
     <row r="222" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="8">
         <f t="shared" si="9"/>
-        <v>3577000</v>
+        <v>3677000</v>
       </c>
       <c r="B222" s="8"/>
       <c r="C222" s="8"/>
@@ -4364,7 +4376,7 @@
     <row r="223" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="8">
         <f t="shared" si="9"/>
-        <v>3577000</v>
+        <v>3677000</v>
       </c>
       <c r="B223" s="8"/>
       <c r="C223" s="8"/>
@@ -4374,7 +4386,7 @@
     <row r="224" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="8">
         <f t="shared" si="9"/>
-        <v>3577000</v>
+        <v>3677000</v>
       </c>
       <c r="B224" s="8"/>
       <c r="C224" s="8"/>
@@ -4384,7 +4396,7 @@
     <row r="225" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="8">
         <f t="shared" si="9"/>
-        <v>3577000</v>
+        <v>3677000</v>
       </c>
       <c r="B225" s="8"/>
       <c r="C225" s="8"/>
@@ -4394,7 +4406,7 @@
     <row r="226" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="8">
         <f t="shared" si="9"/>
-        <v>3577000</v>
+        <v>3677000</v>
       </c>
       <c r="B226" s="8"/>
       <c r="C226" s="8"/>
@@ -4404,7 +4416,7 @@
     <row r="227" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="8">
         <f t="shared" si="9"/>
-        <v>3577000</v>
+        <v>3677000</v>
       </c>
       <c r="B227" s="8"/>
       <c r="C227" s="8"/>
@@ -4414,7 +4426,7 @@
     <row r="228" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="8">
         <f t="shared" si="9"/>
-        <v>3577000</v>
+        <v>3677000</v>
       </c>
       <c r="B228" s="8"/>
       <c r="C228" s="8"/>
@@ -4424,7 +4436,7 @@
     <row r="229" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="8">
         <f t="shared" si="9"/>
-        <v>3577000</v>
+        <v>3677000</v>
       </c>
       <c r="B229" s="8"/>
       <c r="C229" s="8"/>
@@ -4434,7 +4446,7 @@
     <row r="230" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B230" s="9">
         <f>SUM(B210:B229)+B204</f>
-        <v>12775500</v>
+        <v>12875500</v>
       </c>
       <c r="C230" s="9">
         <f>SUM(C210:C229)+C204</f>
@@ -4445,7 +4457,7 @@
     <row r="232" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B232" s="10">
         <f>A229</f>
-        <v>3577000</v>
+        <v>3677000</v>
       </c>
       <c r="C232" s="12" t="s">
         <v>198</v>

--- a/customers/abas.xlsx
+++ b/customers/abas.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="241">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -736,6 +736,12 @@
   </si>
   <si>
     <t>اوسکار</t>
+  </si>
+  <si>
+    <t>1405/06/06</t>
+  </si>
+  <si>
+    <t>سیگار مزه</t>
   </si>
 </sst>
 </file>
@@ -1292,7 +1298,7 @@
       </c>
       <c r="H2" s="9">
         <f>B232</f>
-        <v>3677000</v>
+        <v>4069000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4346,17 +4352,23 @@
     <row r="220" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="8">
         <f t="shared" si="9"/>
-        <v>3677000</v>
-      </c>
-      <c r="B220" s="8"/>
+        <v>4069000</v>
+      </c>
+      <c r="B220" s="8">
+        <v>392000</v>
+      </c>
       <c r="C220" s="8"/>
-      <c r="D220" s="1"/>
-      <c r="E220" s="1"/>
+      <c r="D220" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="E220" s="1" t="s">
+        <v>239</v>
+      </c>
     </row>
     <row r="221" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="8">
         <f t="shared" si="9"/>
-        <v>3677000</v>
+        <v>4069000</v>
       </c>
       <c r="B221" s="8"/>
       <c r="C221" s="8"/>
@@ -4366,7 +4378,7 @@
     <row r="222" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="8">
         <f t="shared" si="9"/>
-        <v>3677000</v>
+        <v>4069000</v>
       </c>
       <c r="B222" s="8"/>
       <c r="C222" s="8"/>
@@ -4376,7 +4388,7 @@
     <row r="223" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="8">
         <f t="shared" si="9"/>
-        <v>3677000</v>
+        <v>4069000</v>
       </c>
       <c r="B223" s="8"/>
       <c r="C223" s="8"/>
@@ -4386,7 +4398,7 @@
     <row r="224" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="8">
         <f t="shared" si="9"/>
-        <v>3677000</v>
+        <v>4069000</v>
       </c>
       <c r="B224" s="8"/>
       <c r="C224" s="8"/>
@@ -4396,7 +4408,7 @@
     <row r="225" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="8">
         <f t="shared" si="9"/>
-        <v>3677000</v>
+        <v>4069000</v>
       </c>
       <c r="B225" s="8"/>
       <c r="C225" s="8"/>
@@ -4406,7 +4418,7 @@
     <row r="226" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="8">
         <f t="shared" si="9"/>
-        <v>3677000</v>
+        <v>4069000</v>
       </c>
       <c r="B226" s="8"/>
       <c r="C226" s="8"/>
@@ -4416,7 +4428,7 @@
     <row r="227" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="8">
         <f t="shared" si="9"/>
-        <v>3677000</v>
+        <v>4069000</v>
       </c>
       <c r="B227" s="8"/>
       <c r="C227" s="8"/>
@@ -4426,7 +4438,7 @@
     <row r="228" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="8">
         <f t="shared" si="9"/>
-        <v>3677000</v>
+        <v>4069000</v>
       </c>
       <c r="B228" s="8"/>
       <c r="C228" s="8"/>
@@ -4436,7 +4448,7 @@
     <row r="229" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="8">
         <f t="shared" si="9"/>
-        <v>3677000</v>
+        <v>4069000</v>
       </c>
       <c r="B229" s="8"/>
       <c r="C229" s="8"/>
@@ -4446,7 +4458,7 @@
     <row r="230" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B230" s="9">
         <f>SUM(B210:B229)+B204</f>
-        <v>12875500</v>
+        <v>13267500</v>
       </c>
       <c r="C230" s="9">
         <f>SUM(C210:C229)+C204</f>
@@ -4457,7 +4469,7 @@
     <row r="232" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B232" s="10">
         <f>A229</f>
-        <v>3677000</v>
+        <v>4069000</v>
       </c>
       <c r="C232" s="12" t="s">
         <v>198</v>

--- a/customers/abas.xlsx
+++ b/customers/abas.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="243">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -742,6 +742,12 @@
   </si>
   <si>
     <t>سیگار مزه</t>
+  </si>
+  <si>
+    <t>1405/06/07</t>
+  </si>
+  <si>
+    <t>دنگ سوسیس خونه یاسین</t>
   </si>
 </sst>
 </file>
@@ -1298,7 +1304,7 @@
       </c>
       <c r="H2" s="9">
         <f>B232</f>
-        <v>4069000</v>
+        <v>2185000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4368,27 +4374,37 @@
     <row r="221" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="8">
         <f t="shared" si="9"/>
-        <v>4069000</v>
-      </c>
-      <c r="B221" s="8"/>
+        <v>4185000</v>
+      </c>
+      <c r="B221" s="8">
+        <v>116000</v>
+      </c>
       <c r="C221" s="8"/>
-      <c r="D221" s="1"/>
-      <c r="E221" s="1"/>
+      <c r="D221" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="E221" s="1" t="s">
+        <v>241</v>
+      </c>
     </row>
     <row r="222" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="8">
         <f t="shared" si="9"/>
-        <v>4069000</v>
+        <v>2185000</v>
       </c>
       <c r="B222" s="8"/>
-      <c r="C222" s="8"/>
-      <c r="D222" s="1"/>
+      <c r="C222" s="8">
+        <v>2000000</v>
+      </c>
+      <c r="D222" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="E222" s="1"/>
     </row>
     <row r="223" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="8">
         <f t="shared" si="9"/>
-        <v>4069000</v>
+        <v>2185000</v>
       </c>
       <c r="B223" s="8"/>
       <c r="C223" s="8"/>
@@ -4398,7 +4414,7 @@
     <row r="224" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="8">
         <f t="shared" si="9"/>
-        <v>4069000</v>
+        <v>2185000</v>
       </c>
       <c r="B224" s="8"/>
       <c r="C224" s="8"/>
@@ -4408,7 +4424,7 @@
     <row r="225" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="8">
         <f t="shared" si="9"/>
-        <v>4069000</v>
+        <v>2185000</v>
       </c>
       <c r="B225" s="8"/>
       <c r="C225" s="8"/>
@@ -4418,7 +4434,7 @@
     <row r="226" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="8">
         <f t="shared" si="9"/>
-        <v>4069000</v>
+        <v>2185000</v>
       </c>
       <c r="B226" s="8"/>
       <c r="C226" s="8"/>
@@ -4428,7 +4444,7 @@
     <row r="227" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="8">
         <f t="shared" si="9"/>
-        <v>4069000</v>
+        <v>2185000</v>
       </c>
       <c r="B227" s="8"/>
       <c r="C227" s="8"/>
@@ -4438,7 +4454,7 @@
     <row r="228" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="8">
         <f t="shared" si="9"/>
-        <v>4069000</v>
+        <v>2185000</v>
       </c>
       <c r="B228" s="8"/>
       <c r="C228" s="8"/>
@@ -4448,7 +4464,7 @@
     <row r="229" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="8">
         <f t="shared" si="9"/>
-        <v>4069000</v>
+        <v>2185000</v>
       </c>
       <c r="B229" s="8"/>
       <c r="C229" s="8"/>
@@ -4458,18 +4474,18 @@
     <row r="230" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B230" s="9">
         <f>SUM(B210:B229)+B204</f>
-        <v>13267500</v>
+        <v>13383500</v>
       </c>
       <c r="C230" s="9">
         <f>SUM(C210:C229)+C204</f>
-        <v>9198500</v>
+        <v>11198500</v>
       </c>
     </row>
     <row r="231" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="232" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B232" s="10">
         <f>A229</f>
-        <v>4069000</v>
+        <v>2185000</v>
       </c>
       <c r="C232" s="12" t="s">
         <v>198</v>

--- a/customers/abas.xlsx
+++ b/customers/abas.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="245">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -748,6 +748,12 @@
   </si>
   <si>
     <t>دنگ سوسیس خونه یاسین</t>
+  </si>
+  <si>
+    <t>1405/06/09</t>
+  </si>
+  <si>
+    <t>مزه پل دوآب</t>
   </si>
 </sst>
 </file>
@@ -1304,7 +1310,7 @@
       </c>
       <c r="H2" s="9">
         <f>B232</f>
-        <v>2185000</v>
+        <v>2405000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4404,27 +4410,37 @@
     <row r="223" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="8">
         <f t="shared" si="9"/>
-        <v>2185000</v>
-      </c>
-      <c r="B223" s="8"/>
+        <v>2355000</v>
+      </c>
+      <c r="B223" s="8">
+        <v>170000</v>
+      </c>
       <c r="C223" s="8"/>
-      <c r="D223" s="1"/>
-      <c r="E223" s="1"/>
+      <c r="D223" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="E223" s="1" t="s">
+        <v>243</v>
+      </c>
     </row>
     <row r="224" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="8">
         <f t="shared" si="9"/>
-        <v>2185000</v>
-      </c>
-      <c r="B224" s="8"/>
+        <v>2405000</v>
+      </c>
+      <c r="B224" s="8">
+        <v>50000</v>
+      </c>
       <c r="C224" s="8"/>
-      <c r="D224" s="1"/>
+      <c r="D224" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="E224" s="1"/>
     </row>
     <row r="225" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="8">
         <f t="shared" si="9"/>
-        <v>2185000</v>
+        <v>2405000</v>
       </c>
       <c r="B225" s="8"/>
       <c r="C225" s="8"/>
@@ -4434,7 +4450,7 @@
     <row r="226" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="8">
         <f t="shared" si="9"/>
-        <v>2185000</v>
+        <v>2405000</v>
       </c>
       <c r="B226" s="8"/>
       <c r="C226" s="8"/>
@@ -4444,7 +4460,7 @@
     <row r="227" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="8">
         <f t="shared" si="9"/>
-        <v>2185000</v>
+        <v>2405000</v>
       </c>
       <c r="B227" s="8"/>
       <c r="C227" s="8"/>
@@ -4454,7 +4470,7 @@
     <row r="228" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="8">
         <f t="shared" si="9"/>
-        <v>2185000</v>
+        <v>2405000</v>
       </c>
       <c r="B228" s="8"/>
       <c r="C228" s="8"/>
@@ -4464,7 +4480,7 @@
     <row r="229" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="8">
         <f t="shared" si="9"/>
-        <v>2185000</v>
+        <v>2405000</v>
       </c>
       <c r="B229" s="8"/>
       <c r="C229" s="8"/>
@@ -4474,7 +4490,7 @@
     <row r="230" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B230" s="9">
         <f>SUM(B210:B229)+B204</f>
-        <v>13383500</v>
+        <v>13603500</v>
       </c>
       <c r="C230" s="9">
         <f>SUM(C210:C229)+C204</f>
@@ -4485,7 +4501,7 @@
     <row r="232" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B232" s="10">
         <f>A229</f>
-        <v>2185000</v>
+        <v>2405000</v>
       </c>
       <c r="C232" s="12" t="s">
         <v>198</v>

--- a/customers/abas.xlsx
+++ b/customers/abas.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="246">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -754,6 +754,9 @@
   </si>
   <si>
     <t>مزه پل دوآب</t>
+  </si>
+  <si>
+    <t>1405/06/13</t>
   </si>
 </sst>
 </file>
@@ -1310,7 +1313,7 @@
       </c>
       <c r="H2" s="9">
         <f>B232</f>
-        <v>2405000</v>
+        <v>2560000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4440,17 +4443,23 @@
     <row r="225" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="8">
         <f t="shared" si="9"/>
-        <v>2405000</v>
-      </c>
-      <c r="B225" s="8"/>
+        <v>2560000</v>
+      </c>
+      <c r="B225" s="8">
+        <v>155000</v>
+      </c>
       <c r="C225" s="8"/>
-      <c r="D225" s="1"/>
-      <c r="E225" s="1"/>
+      <c r="D225" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E225" s="1" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="226" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="8">
         <f t="shared" si="9"/>
-        <v>2405000</v>
+        <v>2560000</v>
       </c>
       <c r="B226" s="8"/>
       <c r="C226" s="8"/>
@@ -4460,7 +4469,7 @@
     <row r="227" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="8">
         <f t="shared" si="9"/>
-        <v>2405000</v>
+        <v>2560000</v>
       </c>
       <c r="B227" s="8"/>
       <c r="C227" s="8"/>
@@ -4470,7 +4479,7 @@
     <row r="228" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="8">
         <f t="shared" si="9"/>
-        <v>2405000</v>
+        <v>2560000</v>
       </c>
       <c r="B228" s="8"/>
       <c r="C228" s="8"/>
@@ -4480,7 +4489,7 @@
     <row r="229" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="8">
         <f t="shared" si="9"/>
-        <v>2405000</v>
+        <v>2560000</v>
       </c>
       <c r="B229" s="8"/>
       <c r="C229" s="8"/>
@@ -4490,7 +4499,7 @@
     <row r="230" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B230" s="9">
         <f>SUM(B210:B229)+B204</f>
-        <v>13603500</v>
+        <v>13758500</v>
       </c>
       <c r="C230" s="9">
         <f>SUM(C210:C229)+C204</f>
@@ -4501,7 +4510,7 @@
     <row r="232" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B232" s="10">
         <f>A229</f>
-        <v>2405000</v>
+        <v>2560000</v>
       </c>
       <c r="C232" s="12" t="s">
         <v>198</v>

--- a/customers/abas.xlsx
+++ b/customers/abas.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="248">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -757,6 +757,12 @@
   </si>
   <si>
     <t>1405/06/13</t>
+  </si>
+  <si>
+    <t>1405/06/16</t>
+  </si>
+  <si>
+    <t>چیپس ابمیوه</t>
   </si>
 </sst>
 </file>
@@ -1313,7 +1319,7 @@
       </c>
       <c r="H2" s="9">
         <f>B232</f>
-        <v>2560000</v>
+        <v>2645000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4459,17 +4465,23 @@
     <row r="226" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="8">
         <f t="shared" si="9"/>
-        <v>2560000</v>
-      </c>
-      <c r="B226" s="8"/>
+        <v>2645000</v>
+      </c>
+      <c r="B226" s="8">
+        <v>85000</v>
+      </c>
       <c r="C226" s="8"/>
-      <c r="D226" s="1"/>
-      <c r="E226" s="1"/>
+      <c r="D226" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="E226" s="1" t="s">
+        <v>246</v>
+      </c>
     </row>
     <row r="227" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="8">
         <f t="shared" si="9"/>
-        <v>2560000</v>
+        <v>2645000</v>
       </c>
       <c r="B227" s="8"/>
       <c r="C227" s="8"/>
@@ -4479,7 +4491,7 @@
     <row r="228" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="8">
         <f t="shared" si="9"/>
-        <v>2560000</v>
+        <v>2645000</v>
       </c>
       <c r="B228" s="8"/>
       <c r="C228" s="8"/>
@@ -4489,7 +4501,7 @@
     <row r="229" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="8">
         <f t="shared" si="9"/>
-        <v>2560000</v>
+        <v>2645000</v>
       </c>
       <c r="B229" s="8"/>
       <c r="C229" s="8"/>
@@ -4499,7 +4511,7 @@
     <row r="230" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B230" s="9">
         <f>SUM(B210:B229)+B204</f>
-        <v>13758500</v>
+        <v>13843500</v>
       </c>
       <c r="C230" s="9">
         <f>SUM(C210:C229)+C204</f>
@@ -4510,7 +4522,7 @@
     <row r="232" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B232" s="10">
         <f>A229</f>
-        <v>2560000</v>
+        <v>2645000</v>
       </c>
       <c r="C232" s="12" t="s">
         <v>198</v>

--- a/customers/abas.xlsx
+++ b/customers/abas.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="250">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -763,6 +763,12 @@
   </si>
   <si>
     <t>چیپس ابمیوه</t>
+  </si>
+  <si>
+    <t>1405/06/18</t>
+  </si>
+  <si>
+    <t>الباقی گول</t>
   </si>
 </sst>
 </file>
@@ -1319,7 +1325,7 @@
       </c>
       <c r="H2" s="9">
         <f>B232</f>
-        <v>2645000</v>
+        <v>2682000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4481,17 +4487,23 @@
     <row r="227" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="8">
         <f t="shared" si="9"/>
-        <v>2645000</v>
-      </c>
-      <c r="B227" s="8"/>
+        <v>2682000</v>
+      </c>
+      <c r="B227" s="8">
+        <v>37000</v>
+      </c>
       <c r="C227" s="8"/>
-      <c r="D227" s="1"/>
-      <c r="E227" s="1"/>
+      <c r="D227" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="E227" s="1" t="s">
+        <v>248</v>
+      </c>
     </row>
     <row r="228" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="8">
         <f t="shared" si="9"/>
-        <v>2645000</v>
+        <v>2682000</v>
       </c>
       <c r="B228" s="8"/>
       <c r="C228" s="8"/>
@@ -4501,7 +4513,7 @@
     <row r="229" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="8">
         <f t="shared" si="9"/>
-        <v>2645000</v>
+        <v>2682000</v>
       </c>
       <c r="B229" s="8"/>
       <c r="C229" s="8"/>
@@ -4511,7 +4523,7 @@
     <row r="230" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B230" s="9">
         <f>SUM(B210:B229)+B204</f>
-        <v>13843500</v>
+        <v>13880500</v>
       </c>
       <c r="C230" s="9">
         <f>SUM(C210:C229)+C204</f>
@@ -4522,7 +4534,7 @@
     <row r="232" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B232" s="10">
         <f>A229</f>
-        <v>2645000</v>
+        <v>2682000</v>
       </c>
       <c r="C232" s="12" t="s">
         <v>198</v>

--- a/customers/abas.xlsx
+++ b/customers/abas.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="252">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -769,6 +769,12 @@
   </si>
   <si>
     <t>الباقی گول</t>
+  </si>
+  <si>
+    <t>1405/06/21</t>
+  </si>
+  <si>
+    <t>بستنی پچ پچ سیگار</t>
   </si>
 </sst>
 </file>
@@ -1325,7 +1331,7 @@
       </c>
       <c r="H2" s="9">
         <f>B232</f>
-        <v>2682000</v>
+        <v>2864000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4503,17 +4509,23 @@
     <row r="228" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="8">
         <f t="shared" si="9"/>
-        <v>2682000</v>
-      </c>
-      <c r="B228" s="8"/>
+        <v>2864000</v>
+      </c>
+      <c r="B228" s="8">
+        <v>182000</v>
+      </c>
       <c r="C228" s="8"/>
-      <c r="D228" s="1"/>
-      <c r="E228" s="1"/>
+      <c r="D228" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="E228" s="1" t="s">
+        <v>250</v>
+      </c>
     </row>
     <row r="229" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="8">
         <f t="shared" si="9"/>
-        <v>2682000</v>
+        <v>2864000</v>
       </c>
       <c r="B229" s="8"/>
       <c r="C229" s="8"/>
@@ -4523,7 +4535,7 @@
     <row r="230" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B230" s="9">
         <f>SUM(B210:B229)+B204</f>
-        <v>13880500</v>
+        <v>14062500</v>
       </c>
       <c r="C230" s="9">
         <f>SUM(C210:C229)+C204</f>
@@ -4534,7 +4546,7 @@
     <row r="232" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B232" s="10">
         <f>A229</f>
-        <v>2682000</v>
+        <v>2864000</v>
       </c>
       <c r="C232" s="12" t="s">
         <v>198</v>

--- a/customers/abas.xlsx
+++ b/customers/abas.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="254">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -775,6 +775,12 @@
   </si>
   <si>
     <t>بستنی پچ پچ سیگار</t>
+  </si>
+  <si>
+    <t xml:space="preserve">دنگ سس </t>
+  </si>
+  <si>
+    <t>دنپ کشمش</t>
   </si>
 </sst>
 </file>
@@ -890,7 +896,28 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="18">
+  <dxfs count="21">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1330,8 +1357,8 @@
         <v>7</v>
       </c>
       <c r="H2" s="9">
-        <f>B232</f>
-        <v>2864000</v>
+        <f>B257</f>
+        <v>3190000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4525,17 +4552,21 @@
     <row r="229" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="8">
         <f t="shared" si="9"/>
-        <v>2864000</v>
-      </c>
-      <c r="B229" s="8"/>
+        <v>2960000</v>
+      </c>
+      <c r="B229" s="8">
+        <v>96000</v>
+      </c>
       <c r="C229" s="8"/>
-      <c r="D229" s="1"/>
+      <c r="D229" s="1" t="s">
+        <v>252</v>
+      </c>
       <c r="E229" s="1"/>
     </row>
     <row r="230" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B230" s="9">
         <f>SUM(B210:B229)+B204</f>
-        <v>14062500</v>
+        <v>14158500</v>
       </c>
       <c r="C230" s="9">
         <f>SUM(C210:C229)+C204</f>
@@ -4546,54 +4577,276 @@
     <row r="232" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B232" s="10">
         <f>A229</f>
-        <v>2864000</v>
+        <v>2960000</v>
       </c>
       <c r="C232" s="12" t="s">
         <v>198</v>
       </c>
       <c r="D232" s="12"/>
     </row>
-    <row r="233" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B233" t="s">
-        <v>88</v>
-      </c>
-      <c r="D233" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="234" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="235" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="236" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="237" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="238" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="239" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="240" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="241" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="242" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="243" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="244" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="245" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="246" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="247" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="248" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="249" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="250" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="251" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="252" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="253" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="254" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="255" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="256" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="257" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="258" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="259" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="260" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="261" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="262" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="263" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="264" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="233" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A233" t="s">
+        <v>10</v>
+      </c>
+      <c r="B233" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C233" s="2"/>
+    </row>
+    <row r="234" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A234" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B234" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C234" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D234" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E234" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A235" s="8">
+        <f>B232+B235-C235</f>
+        <v>3190000</v>
+      </c>
+      <c r="B235" s="8">
+        <v>230000</v>
+      </c>
+      <c r="C235" s="8"/>
+      <c r="D235" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="E235" s="1" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A236" s="8">
+        <f>A235+B236-C236</f>
+        <v>3190000</v>
+      </c>
+      <c r="B236" s="8"/>
+      <c r="C236" s="8"/>
+      <c r="D236" s="1"/>
+      <c r="E236" s="1"/>
+    </row>
+    <row r="237" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A237" s="8">
+        <f t="shared" ref="A237:A254" si="10">A236+B237-C237</f>
+        <v>3190000</v>
+      </c>
+      <c r="B237" s="8"/>
+      <c r="C237" s="8"/>
+      <c r="D237" s="1"/>
+      <c r="E237" s="1"/>
+    </row>
+    <row r="238" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A238" s="8">
+        <f t="shared" si="10"/>
+        <v>3190000</v>
+      </c>
+      <c r="B238" s="8"/>
+      <c r="C238" s="8"/>
+      <c r="D238" s="1"/>
+      <c r="E238" s="1"/>
+    </row>
+    <row r="239" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A239" s="8">
+        <f t="shared" si="10"/>
+        <v>3190000</v>
+      </c>
+      <c r="B239" s="8"/>
+      <c r="C239" s="8"/>
+      <c r="D239" s="1"/>
+      <c r="E239" s="1"/>
+    </row>
+    <row r="240" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A240" s="8">
+        <f t="shared" si="10"/>
+        <v>3190000</v>
+      </c>
+      <c r="B240" s="8"/>
+      <c r="C240" s="8"/>
+      <c r="D240" s="1"/>
+      <c r="E240" s="1"/>
+    </row>
+    <row r="241" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A241" s="8">
+        <f t="shared" si="10"/>
+        <v>3190000</v>
+      </c>
+      <c r="B241" s="8"/>
+      <c r="C241" s="8"/>
+      <c r="D241" s="1"/>
+      <c r="E241" s="1"/>
+    </row>
+    <row r="242" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A242" s="8">
+        <f t="shared" si="10"/>
+        <v>3190000</v>
+      </c>
+      <c r="B242" s="8"/>
+      <c r="C242" s="8"/>
+      <c r="D242" s="1"/>
+      <c r="E242" s="1"/>
+    </row>
+    <row r="243" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A243" s="8">
+        <f t="shared" si="10"/>
+        <v>3190000</v>
+      </c>
+      <c r="B243" s="8"/>
+      <c r="C243" s="8"/>
+      <c r="D243" s="1"/>
+      <c r="E243" s="1"/>
+    </row>
+    <row r="244" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A244" s="8">
+        <f t="shared" si="10"/>
+        <v>3190000</v>
+      </c>
+      <c r="B244" s="8"/>
+      <c r="C244" s="8"/>
+      <c r="D244" s="1"/>
+      <c r="E244" s="1"/>
+    </row>
+    <row r="245" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A245" s="8">
+        <f t="shared" si="10"/>
+        <v>3190000</v>
+      </c>
+      <c r="B245" s="8"/>
+      <c r="C245" s="8"/>
+      <c r="D245" s="1"/>
+      <c r="E245" s="1"/>
+    </row>
+    <row r="246" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A246" s="8">
+        <f t="shared" si="10"/>
+        <v>3190000</v>
+      </c>
+      <c r="B246" s="8"/>
+      <c r="C246" s="8"/>
+      <c r="D246" s="1"/>
+      <c r="E246" s="1"/>
+    </row>
+    <row r="247" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A247" s="8">
+        <f t="shared" si="10"/>
+        <v>3190000</v>
+      </c>
+      <c r="B247" s="8"/>
+      <c r="C247" s="8"/>
+      <c r="D247" s="1"/>
+      <c r="E247" s="1"/>
+    </row>
+    <row r="248" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A248" s="8">
+        <f t="shared" si="10"/>
+        <v>3190000</v>
+      </c>
+      <c r="B248" s="8"/>
+      <c r="C248" s="8"/>
+      <c r="D248" s="1"/>
+      <c r="E248" s="1"/>
+    </row>
+    <row r="249" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A249" s="8">
+        <f t="shared" si="10"/>
+        <v>3190000</v>
+      </c>
+      <c r="B249" s="8"/>
+      <c r="C249" s="8"/>
+      <c r="D249" s="1"/>
+      <c r="E249" s="1"/>
+    </row>
+    <row r="250" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A250" s="8">
+        <f t="shared" si="10"/>
+        <v>3190000</v>
+      </c>
+      <c r="B250" s="8"/>
+      <c r="C250" s="8"/>
+      <c r="D250" s="1"/>
+      <c r="E250" s="1"/>
+    </row>
+    <row r="251" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A251" s="8">
+        <f t="shared" si="10"/>
+        <v>3190000</v>
+      </c>
+      <c r="B251" s="8"/>
+      <c r="C251" s="8"/>
+      <c r="D251" s="1"/>
+      <c r="E251" s="1"/>
+    </row>
+    <row r="252" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A252" s="8">
+        <f t="shared" si="10"/>
+        <v>3190000</v>
+      </c>
+      <c r="B252" s="8"/>
+      <c r="C252" s="8"/>
+      <c r="D252" s="1"/>
+      <c r="E252" s="1"/>
+    </row>
+    <row r="253" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A253" s="8">
+        <f t="shared" si="10"/>
+        <v>3190000</v>
+      </c>
+      <c r="B253" s="8"/>
+      <c r="C253" s="8"/>
+      <c r="D253" s="1"/>
+      <c r="E253" s="1"/>
+    </row>
+    <row r="254" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A254" s="8">
+        <f t="shared" si="10"/>
+        <v>3190000</v>
+      </c>
+      <c r="B254" s="8"/>
+      <c r="C254" s="8"/>
+      <c r="D254" s="1"/>
+      <c r="E254" s="1"/>
+    </row>
+    <row r="255" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B255" s="9">
+        <f>SUM(B235:B254)+B230</f>
+        <v>14388500</v>
+      </c>
+      <c r="C255" s="9">
+        <f>SUM(C235:C254)+C230</f>
+        <v>11198500</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="257" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B257" s="10">
+        <f>A254</f>
+        <v>3190000</v>
+      </c>
+      <c r="C257" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="D257" s="12"/>
+    </row>
+    <row r="258" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="259" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="260" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="261" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="262" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="263" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="264" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
+    <mergeCell ref="C257:D257"/>
     <mergeCell ref="C232:D232"/>
     <mergeCell ref="C102:D102"/>
     <mergeCell ref="C128:D128"/>
@@ -4602,17 +4855,28 @@
     <mergeCell ref="C206:D206"/>
   </mergeCells>
   <conditionalFormatting sqref="B102">
-    <cfRule type="cellIs" dxfId="17" priority="18" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="20" priority="21" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="19" priority="20" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="18" priority="19" operator="lessThanOrEqual">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B128">
+    <cfRule type="cellIs" dxfId="17" priority="16" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="16" priority="17" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="16" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="15" priority="18" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B128">
+  <conditionalFormatting sqref="B154">
     <cfRule type="cellIs" dxfId="14" priority="13" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4623,7 +4887,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B154">
+  <conditionalFormatting sqref="B180">
     <cfRule type="cellIs" dxfId="11" priority="10" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4634,7 +4898,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B180">
+  <conditionalFormatting sqref="B206">
     <cfRule type="cellIs" dxfId="8" priority="7" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4645,7 +4909,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B206">
+  <conditionalFormatting sqref="B232">
     <cfRule type="cellIs" dxfId="5" priority="4" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4656,7 +4920,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B232">
+  <conditionalFormatting sqref="B257">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
